--- a/Design Files/Control-Board-v1.0/BOM/eSpark-BOM-Control-Board-v1.0.xlsx
+++ b/Design Files/Control-Board-v1.0/BOM/eSpark-BOM-Control-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="606">
   <si>
     <t>Component list</t>
   </si>
@@ -514,9 +514,6 @@
   </si>
   <si>
     <t>TVS DIODE 5V 9.8V SOD923</t>
-  </si>
-  <si>
-    <t>TVS SURGE PROTECTOR 1-CH 3.3V</t>
   </si>
   <si>
     <t>TVS DIODE 28VWM 45.4VC SMB</t>
@@ -769,9 +766,6 @@
     <t>SOD-923.</t>
   </si>
   <si>
-    <t>SOD-123</t>
-  </si>
-  <si>
     <t>SMB_</t>
   </si>
   <si>
@@ -982,9 +976,6 @@
     <t>ESD9L5.0ST5G</t>
   </si>
   <si>
-    <t>AZ3003-01G</t>
-  </si>
-  <si>
     <t>SMBJ28A-13-F</t>
   </si>
   <si>
@@ -1198,9 +1189,6 @@
     <t>ON Semiconductor</t>
   </si>
   <si>
-    <t>Amazing</t>
-  </si>
-  <si>
     <t>Diodes</t>
   </si>
   <si>
@@ -1835,6 +1823,21 @@
   </si>
   <si>
     <t>-------</t>
+  </si>
+  <si>
+    <t>20A 350W 16V 4V 3.3V SOD-323 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>SOD-323</t>
+  </si>
+  <si>
+    <t>SD03</t>
+  </si>
+  <si>
+    <t>C502526</t>
+  </si>
+  <si>
+    <t>------</t>
   </si>
 </sst>
 </file>
@@ -2274,17 +2277,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2317,6 +2309,17 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2639,14 +2642,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2657,7 +2660,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="40" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -2681,7 +2684,7 @@
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="41" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="30"/>
@@ -2771,43 +2774,43 @@
         <v>137</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="I7" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="O7" s="12" t="s">
         <v>583</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>434</v>
-      </c>
-      <c r="K7" s="12" t="s">
+      <c r="P7" s="12" t="s">
         <v>584</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>580</v>
-      </c>
-      <c r="M7" s="12" t="s">
+      <c r="Q7" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="R7" s="12" t="s">
         <v>586</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>587</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>588</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>589</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -2826,22 +2829,22 @@
         <v>138</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I8" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I8" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="L8" s="14">
         <v>2</v>
@@ -2853,8 +2856,8 @@
       <c r="N8" s="14">
         <v>20</v>
       </c>
-      <c r="O8" s="51" t="s">
-        <v>600</v>
+      <c r="O8" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P8" s="15">
         <v>2.0799999999999999E-2</v>
@@ -2881,22 +2884,22 @@
         <v>139</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="I9" s="54" t="s">
-        <v>604</v>
+        <v>381</v>
+      </c>
+      <c r="I9" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="K9" s="20" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="L9" s="20">
         <v>2</v>
@@ -2908,8 +2911,8 @@
       <c r="N9" s="20">
         <v>20</v>
       </c>
-      <c r="O9" s="51" t="s">
-        <v>600</v>
+      <c r="O9" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P9" s="21">
         <v>3.7400000000000003E-2</v>
@@ -2936,22 +2939,22 @@
         <v>140</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I10" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I10" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="L10" s="14">
         <v>9</v>
@@ -2963,8 +2966,8 @@
       <c r="N10" s="14">
         <v>100</v>
       </c>
-      <c r="O10" s="51" t="s">
-        <v>600</v>
+      <c r="O10" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P10" s="15">
         <v>1.6000000000000001E-3</v>
@@ -2991,22 +2994,22 @@
         <v>141</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I11" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="L11" s="20">
         <v>2</v>
@@ -3018,8 +3021,8 @@
       <c r="N11" s="20">
         <v>50</v>
       </c>
-      <c r="O11" s="51" t="s">
-        <v>600</v>
+      <c r="O11" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P11" s="21">
         <v>1.7500000000000002E-2</v>
@@ -3046,22 +3049,22 @@
         <v>142</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="I12" s="54" t="s">
-        <v>604</v>
+        <v>382</v>
+      </c>
+      <c r="I12" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="L12" s="14">
         <v>11</v>
@@ -3073,8 +3076,8 @@
       <c r="N12" s="14">
         <v>60</v>
       </c>
-      <c r="O12" s="51" t="s">
-        <v>600</v>
+      <c r="O12" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P12" s="15">
         <v>1.32E-2</v>
@@ -3094,51 +3097,51 @@
       <c r="C13" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="F13" s="48" t="s">
-        <v>244</v>
-      </c>
-      <c r="G13" s="45" t="s">
-        <v>299</v>
+      <c r="F13" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>297</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I13" s="55" t="s">
-        <v>604</v>
-      </c>
-      <c r="J13" s="45" t="s">
-        <v>440</v>
-      </c>
-      <c r="K13" s="45" t="s">
-        <v>534</v>
-      </c>
-      <c r="L13" s="45">
+        <v>380</v>
+      </c>
+      <c r="I13" s="52" t="s">
+        <v>600</v>
+      </c>
+      <c r="J13" s="42" t="s">
+        <v>436</v>
+      </c>
+      <c r="K13" s="42" t="s">
+        <v>530</v>
+      </c>
+      <c r="L13" s="42">
         <v>2</v>
       </c>
-      <c r="M13" s="47">
+      <c r="M13" s="44">
         <f t="shared" ref="M13" si="5">L13*5</f>
         <v>10</v>
       </c>
-      <c r="N13" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="O13" s="47" t="s">
-        <v>600</v>
-      </c>
-      <c r="P13" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q13" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="R13" s="50" t="s">
-        <v>591</v>
+      <c r="N13" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="O13" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="P13" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q13" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="R13" s="47" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -3157,22 +3160,22 @@
         <v>144</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I14" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I14" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="L14" s="14">
         <v>2</v>
@@ -3184,8 +3187,8 @@
       <c r="N14" s="14">
         <v>100</v>
       </c>
-      <c r="O14" s="51" t="s">
-        <v>600</v>
+      <c r="O14" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P14" s="15">
         <v>1E-3</v>
@@ -3212,22 +3215,22 @@
         <v>145</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="I15" s="54" t="s">
-        <v>604</v>
+        <v>383</v>
+      </c>
+      <c r="I15" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="L15" s="20">
         <v>2</v>
@@ -3239,8 +3242,8 @@
       <c r="N15" s="20">
         <v>20</v>
       </c>
-      <c r="O15" s="51" t="s">
-        <v>600</v>
+      <c r="O15" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P15" s="21">
         <v>2.2800000000000001E-2</v>
@@ -3267,22 +3270,22 @@
         <v>146</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="I16" s="54" t="s">
-        <v>604</v>
+        <v>382</v>
+      </c>
+      <c r="I16" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="L16" s="14">
         <v>2</v>
@@ -3294,8 +3297,8 @@
       <c r="N16" s="14">
         <v>11</v>
       </c>
-      <c r="O16" s="51" t="s">
-        <v>600</v>
+      <c r="O16" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P16" s="15">
         <v>1.0296000000000001</v>
@@ -3322,22 +3325,22 @@
         <v>143</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I17" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I17" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="L17" s="20">
         <v>1</v>
@@ -3349,8 +3352,8 @@
       <c r="N17" s="20">
         <v>100</v>
       </c>
-      <c r="O17" s="51" t="s">
-        <v>600</v>
+      <c r="O17" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P17" s="21">
         <v>1.4E-3</v>
@@ -3377,22 +3380,22 @@
         <v>147</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I18" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I18" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="L18" s="14">
         <v>2</v>
@@ -3404,8 +3407,8 @@
       <c r="N18" s="14">
         <v>100</v>
       </c>
-      <c r="O18" s="51" t="s">
-        <v>600</v>
+      <c r="O18" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P18" s="15">
         <v>1E-3</v>
@@ -3432,22 +3435,22 @@
         <v>148</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="I19" s="54" t="s">
-        <v>604</v>
+        <v>381</v>
+      </c>
+      <c r="I19" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="L19" s="20">
         <v>7</v>
@@ -3459,8 +3462,8 @@
       <c r="N19" s="20">
         <v>50</v>
       </c>
-      <c r="O19" s="51" t="s">
-        <v>600</v>
+      <c r="O19" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P19" s="21">
         <v>8.3999999999999995E-3</v>
@@ -3487,22 +3490,22 @@
         <v>149</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="I20" s="54" t="s">
-        <v>604</v>
+        <v>382</v>
+      </c>
+      <c r="I20" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="L20" s="14">
         <v>8</v>
@@ -3514,8 +3517,8 @@
       <c r="N20" s="14">
         <v>45</v>
       </c>
-      <c r="O20" s="51" t="s">
-        <v>600</v>
+      <c r="O20" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P20" s="15">
         <v>9.4500000000000001E-2</v>
@@ -3542,22 +3545,22 @@
         <v>150</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I21" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I21" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="L21" s="20">
         <v>4</v>
@@ -3569,8 +3572,8 @@
       <c r="N21" s="20">
         <v>100</v>
       </c>
-      <c r="O21" s="51" t="s">
-        <v>600</v>
+      <c r="O21" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P21" s="21">
         <v>2.5999999999999999E-3</v>
@@ -3597,22 +3600,22 @@
         <v>151</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="I22" s="54" t="s">
-        <v>604</v>
+        <v>384</v>
+      </c>
+      <c r="I22" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="L22" s="14">
         <v>1</v>
@@ -3624,8 +3627,8 @@
       <c r="N22" s="14">
         <v>10</v>
       </c>
-      <c r="O22" s="51" t="s">
-        <v>600</v>
+      <c r="O22" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P22" s="15">
         <v>3.7000000000000002E-3</v>
@@ -3652,22 +3655,22 @@
         <v>152</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="I23" s="54" t="s">
-        <v>604</v>
+        <v>381</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="L23" s="20">
         <v>2</v>
@@ -3679,8 +3682,8 @@
       <c r="N23" s="20">
         <v>20</v>
       </c>
-      <c r="O23" s="51" t="s">
-        <v>600</v>
+      <c r="O23" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P23" s="21">
         <v>1.83E-2</v>
@@ -3700,51 +3703,51 @@
       <c r="C24" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="46" t="s">
+      <c r="E24" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="F24" s="48" t="s">
-        <v>244</v>
-      </c>
-      <c r="G24" s="45" t="s">
-        <v>308</v>
+      <c r="F24" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="G24" s="42" t="s">
+        <v>306</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="I24" s="55" t="s">
-        <v>604</v>
-      </c>
-      <c r="J24" s="45" t="s">
-        <v>449</v>
-      </c>
-      <c r="K24" s="45" t="s">
-        <v>534</v>
-      </c>
-      <c r="L24" s="45">
+        <v>381</v>
+      </c>
+      <c r="I24" s="52" t="s">
+        <v>600</v>
+      </c>
+      <c r="J24" s="42" t="s">
+        <v>445</v>
+      </c>
+      <c r="K24" s="42" t="s">
+        <v>530</v>
+      </c>
+      <c r="L24" s="42">
         <v>8</v>
       </c>
-      <c r="M24" s="47">
+      <c r="M24" s="44">
         <f>L24*5</f>
         <v>40</v>
       </c>
-      <c r="N24" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="O24" s="47" t="s">
-        <v>600</v>
-      </c>
-      <c r="P24" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q24" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="R24" s="50" t="s">
-        <v>591</v>
+      <c r="N24" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="O24" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="P24" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q24" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="R24" s="47" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -3763,22 +3766,22 @@
         <v>154</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I25" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="K25" s="20" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="L25" s="20">
         <v>2</v>
@@ -3790,8 +3793,8 @@
       <c r="N25" s="20">
         <v>100</v>
       </c>
-      <c r="O25" s="51" t="s">
-        <v>600</v>
+      <c r="O25" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P25" s="21">
         <v>3.0999999999999999E-3</v>
@@ -3818,22 +3821,22 @@
         <v>155</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="I26" s="54" t="s">
-        <v>604</v>
+        <v>385</v>
+      </c>
+      <c r="I26" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="L26" s="14">
         <v>3</v>
@@ -3845,8 +3848,8 @@
       <c r="N26" s="14">
         <v>20</v>
       </c>
-      <c r="O26" s="51" t="s">
-        <v>600</v>
+      <c r="O26" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P26" s="15">
         <v>0.29310000000000003</v>
@@ -3873,22 +3876,22 @@
         <v>156</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="I27" s="54" t="s">
-        <v>604</v>
+        <v>386</v>
+      </c>
+      <c r="I27" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="L27" s="20">
         <v>1</v>
@@ -3900,8 +3903,8 @@
       <c r="N27" s="20">
         <v>10</v>
       </c>
-      <c r="O27" s="51" t="s">
-        <v>600</v>
+      <c r="O27" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P27" s="21">
         <v>0.17219999999999999</v>
@@ -3928,22 +3931,22 @@
         <v>157</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I28" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I28" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="L28" s="14">
         <v>1</v>
@@ -3955,8 +3958,8 @@
       <c r="N28" s="14">
         <v>10</v>
       </c>
-      <c r="O28" s="51" t="s">
-        <v>600</v>
+      <c r="O28" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P28" s="15">
         <v>6.83E-2</v>
@@ -3983,22 +3986,22 @@
         <v>158</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I29" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I29" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="L29" s="20">
         <v>2</v>
@@ -4010,8 +4013,8 @@
       <c r="N29" s="20">
         <v>15</v>
       </c>
-      <c r="O29" s="51" t="s">
-        <v>600</v>
+      <c r="O29" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P29" s="21">
         <v>0.14480000000000001</v>
@@ -4038,22 +4041,22 @@
         <v>159</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>390</v>
-      </c>
-      <c r="I30" s="54" t="s">
-        <v>604</v>
+        <v>387</v>
+      </c>
+      <c r="I30" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="L30" s="14">
         <v>2</v>
@@ -4065,8 +4068,8 @@
       <c r="N30" s="14">
         <v>100</v>
       </c>
-      <c r="O30" s="51" t="s">
-        <v>600</v>
+      <c r="O30" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P30" s="15">
         <v>2.8E-3</v>
@@ -4093,22 +4096,22 @@
         <v>160</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I31" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I31" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="K31" s="20" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="L31" s="20">
         <v>2</v>
@@ -4120,8 +4123,8 @@
       <c r="N31" s="20">
         <v>50</v>
       </c>
-      <c r="O31" s="51" t="s">
-        <v>600</v>
+      <c r="O31" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P31" s="21">
         <v>1.4E-2</v>
@@ -4148,22 +4151,22 @@
         <v>161</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I32" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I32" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="L32" s="14">
         <v>1</v>
@@ -4175,8 +4178,8 @@
       <c r="N32" s="14">
         <v>100</v>
       </c>
-      <c r="O32" s="51" t="s">
-        <v>600</v>
+      <c r="O32" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P32" s="15">
         <v>2.8E-3</v>
@@ -4203,22 +4206,22 @@
         <v>162</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I33" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I33" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K33" s="20" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="L33" s="20">
         <v>2</v>
@@ -4230,8 +4233,8 @@
       <c r="N33" s="20">
         <v>100</v>
       </c>
-      <c r="O33" s="51" t="s">
-        <v>600</v>
+      <c r="O33" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P33" s="21">
         <v>2.5999999999999999E-3</v>
@@ -4258,22 +4261,22 @@
         <v>163</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I34" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I34" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="L34" s="14">
         <v>1</v>
@@ -4285,8 +4288,8 @@
       <c r="N34" s="14">
         <v>50</v>
       </c>
-      <c r="O34" s="51" t="s">
-        <v>600</v>
+      <c r="O34" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P34" s="15">
         <v>1.1900000000000001E-2</v>
@@ -4313,22 +4316,22 @@
         <v>164</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="I35" s="54" t="s">
-        <v>604</v>
+        <v>388</v>
+      </c>
+      <c r="I35" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="K35" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L35" s="20">
         <v>4</v>
@@ -4340,8 +4343,8 @@
       <c r="N35" s="20">
         <v>25</v>
       </c>
-      <c r="O35" s="51" t="s">
-        <v>600</v>
+      <c r="O35" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P35" s="21">
         <v>0.10249999999999999</v>
@@ -4352,7 +4355,7 @@
       </c>
       <c r="R35" s="20"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="16">
         <f>ROW(B36) - ROW($B$7)</f>
@@ -4364,26 +4367,26 @@
       <c r="D36" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E36" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="H36" s="14" t="s">
+      <c r="E36" s="20" t="s">
+        <v>601</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="H36" s="20" t="s">
         <v>392</v>
       </c>
-      <c r="I36" s="54" t="s">
+      <c r="I36" s="51" t="s">
+        <v>605</v>
+      </c>
+      <c r="J36" s="20" t="s">
         <v>604</v>
       </c>
-      <c r="J36" s="14" t="s">
-        <v>461</v>
-      </c>
       <c r="K36" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L36" s="14">
         <v>2</v>
@@ -4392,14 +4395,18 @@
         <f>L36*5</f>
         <v>10</v>
       </c>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14" t="s">
-        <v>600</v>
-      </c>
-      <c r="P36" s="15"/>
+      <c r="N36" s="20">
+        <v>20</v>
+      </c>
+      <c r="O36" s="48" t="s">
+        <v>596</v>
+      </c>
+      <c r="P36" s="21">
+        <v>2.4E-2</v>
+      </c>
       <c r="Q36" s="15">
         <f>P36*N36</f>
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="R36" s="14"/>
     </row>
@@ -4416,25 +4423,25 @@
         <v>60</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="I37" s="54" t="s">
-        <v>604</v>
+        <v>389</v>
+      </c>
+      <c r="I37" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="K37" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L37" s="20">
         <v>1</v>
@@ -4446,8 +4453,8 @@
       <c r="N37" s="20">
         <v>10</v>
       </c>
-      <c r="O37" s="51" t="s">
-        <v>600</v>
+      <c r="O37" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P37" s="21">
         <v>0.153</v>
@@ -4471,25 +4478,25 @@
         <v>61</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>394</v>
-      </c>
-      <c r="I38" s="54" t="s">
-        <v>604</v>
+        <v>390</v>
+      </c>
+      <c r="I38" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="K38" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L38" s="14">
         <v>1</v>
@@ -4501,8 +4508,8 @@
       <c r="N38" s="14">
         <v>20</v>
       </c>
-      <c r="O38" s="51" t="s">
-        <v>600</v>
+      <c r="O38" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P38" s="15">
         <v>3.0800000000000001E-2</v>
@@ -4526,25 +4533,25 @@
         <v>62</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="I39" s="54" t="s">
-        <v>604</v>
+        <v>391</v>
+      </c>
+      <c r="I39" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="K39" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L39" s="20">
         <v>8</v>
@@ -4556,8 +4563,8 @@
       <c r="N39" s="20">
         <v>50</v>
       </c>
-      <c r="O39" s="51" t="s">
-        <v>600</v>
+      <c r="O39" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P39" s="21">
         <v>2.6700000000000002E-2</v>
@@ -4581,25 +4588,25 @@
         <v>63</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="I40" s="54" t="s">
-        <v>604</v>
+        <v>392</v>
+      </c>
+      <c r="I40" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="K40" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L40" s="14">
         <v>1</v>
@@ -4611,8 +4618,8 @@
       <c r="N40" s="14">
         <v>10</v>
       </c>
-      <c r="O40" s="51" t="s">
-        <v>600</v>
+      <c r="O40" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P40" s="15">
         <v>4.53E-2</v>
@@ -4636,25 +4643,25 @@
         <v>64</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>397</v>
-      </c>
-      <c r="I41" s="54" t="s">
-        <v>604</v>
+        <v>393</v>
+      </c>
+      <c r="I41" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="K41" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L41" s="20">
         <v>1</v>
@@ -4666,8 +4673,8 @@
       <c r="N41" s="20">
         <v>20</v>
       </c>
-      <c r="O41" s="51" t="s">
-        <v>600</v>
+      <c r="O41" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P41" s="21">
         <v>1.9300000000000001E-2</v>
@@ -4691,25 +4698,25 @@
         <v>65</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="I42" s="54" t="s">
-        <v>604</v>
+        <v>394</v>
+      </c>
+      <c r="I42" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="K42" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L42" s="14">
         <v>8</v>
@@ -4721,8 +4728,8 @@
       <c r="N42" s="14">
         <v>50</v>
       </c>
-      <c r="O42" s="51" t="s">
-        <v>600</v>
+      <c r="O42" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P42" s="15">
         <v>5.5500000000000001E-2</v>
@@ -4746,25 +4753,25 @@
         <v>66</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="I43" s="54" t="s">
-        <v>604</v>
+        <v>381</v>
+      </c>
+      <c r="I43" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="K43" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L43" s="20">
         <v>2</v>
@@ -4776,8 +4783,8 @@
       <c r="N43" s="20">
         <v>50</v>
       </c>
-      <c r="O43" s="51" t="s">
-        <v>600</v>
+      <c r="O43" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P43" s="21">
         <v>7.0000000000000001E-3</v>
@@ -4801,25 +4808,25 @@
         <v>67</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>399</v>
-      </c>
-      <c r="I44" s="54" t="s">
-        <v>604</v>
+        <v>395</v>
+      </c>
+      <c r="I44" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="K44" s="14" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="L44" s="14">
         <v>2</v>
@@ -4831,8 +4838,8 @@
       <c r="N44" s="14">
         <v>50</v>
       </c>
-      <c r="O44" s="51" t="s">
-        <v>600</v>
+      <c r="O44" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P44" s="15">
         <v>1.52E-2</v>
@@ -4856,25 +4863,25 @@
         <v>68</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>400</v>
-      </c>
-      <c r="I45" s="54" t="s">
-        <v>604</v>
+        <v>396</v>
+      </c>
+      <c r="I45" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J45" s="20" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="K45" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L45" s="20">
         <v>2</v>
@@ -4886,8 +4893,8 @@
       <c r="N45" s="20">
         <v>15</v>
       </c>
-      <c r="O45" s="51" t="s">
-        <v>600</v>
+      <c r="O45" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P45" s="21">
         <v>0.1482</v>
@@ -4911,25 +4918,25 @@
         <v>69</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="I46" s="54" t="s">
-        <v>604</v>
+        <v>397</v>
+      </c>
+      <c r="I46" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L46" s="14">
         <v>4</v>
@@ -4941,8 +4948,8 @@
       <c r="N46" s="14">
         <v>50</v>
       </c>
-      <c r="O46" s="51" t="s">
-        <v>600</v>
+      <c r="O46" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P46" s="15">
         <v>1.6899999999999998E-2</v>
@@ -4966,25 +4973,25 @@
         <v>70</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="I47" s="54" t="s">
-        <v>604</v>
+        <v>398</v>
+      </c>
+      <c r="I47" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J47" s="20" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="K47" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L47" s="20">
         <v>1</v>
@@ -4996,8 +5003,8 @@
       <c r="N47" s="20">
         <v>12</v>
       </c>
-      <c r="O47" s="51" t="s">
-        <v>600</v>
+      <c r="O47" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P47" s="21">
         <v>6.4100000000000004E-2</v>
@@ -5021,25 +5028,25 @@
         <v>71</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="I48" s="54" t="s">
-        <v>604</v>
+        <v>399</v>
+      </c>
+      <c r="I48" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="K48" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L48" s="14">
         <v>2</v>
@@ -5051,8 +5058,8 @@
       <c r="N48" s="14">
         <v>20</v>
       </c>
-      <c r="O48" s="51" t="s">
-        <v>600</v>
+      <c r="O48" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P48" s="15">
         <v>5.1299999999999998E-2</v>
@@ -5076,25 +5083,25 @@
         <v>72</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="G49" s="47" t="s">
-        <v>550</v>
+        <v>257</v>
+      </c>
+      <c r="G49" s="44" t="s">
+        <v>546</v>
       </c>
       <c r="H49" s="14" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="I49" s="20" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="K49" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L49" s="20">
         <v>1</v>
@@ -5106,8 +5113,8 @@
       <c r="N49" s="14">
         <v>50</v>
       </c>
-      <c r="O49" s="53" t="s">
-        <v>600</v>
+      <c r="O49" s="50" t="s">
+        <v>596</v>
       </c>
       <c r="P49" s="15">
         <v>1.4500000000000001E-2</v>
@@ -5131,25 +5138,25 @@
         <v>73</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="I50" s="54" t="s">
-        <v>604</v>
+        <v>399</v>
+      </c>
+      <c r="I50" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="K50" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L50" s="14">
         <v>1</v>
@@ -5161,8 +5168,8 @@
       <c r="N50" s="14">
         <v>10</v>
       </c>
-      <c r="O50" s="51" t="s">
-        <v>600</v>
+      <c r="O50" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P50" s="15">
         <v>8.0100000000000005E-2</v>
@@ -5186,25 +5193,25 @@
         <v>74</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>403</v>
-      </c>
-      <c r="I51" s="54" t="s">
-        <v>604</v>
+        <v>399</v>
+      </c>
+      <c r="I51" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J51" s="20" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="K51" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L51" s="20">
         <v>1</v>
@@ -5216,8 +5223,8 @@
       <c r="N51" s="20">
         <v>10</v>
       </c>
-      <c r="O51" s="51" t="s">
-        <v>600</v>
+      <c r="O51" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P51" s="21">
         <v>0.16259999999999999</v>
@@ -5241,25 +5248,25 @@
         <v>75</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G52" s="14">
         <v>1715721</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="I52" s="54" t="s">
-        <v>604</v>
+        <v>400</v>
+      </c>
+      <c r="I52" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="K52" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L52" s="14">
         <v>5</v>
@@ -5271,8 +5278,8 @@
       <c r="N52" s="14">
         <v>26</v>
       </c>
-      <c r="O52" s="51" t="s">
-        <v>600</v>
+      <c r="O52" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P52" s="15">
         <v>0.30509999999999998</v>
@@ -5296,25 +5303,25 @@
         <v>76</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>401</v>
-      </c>
-      <c r="I53" s="54" t="s">
-        <v>604</v>
+        <v>397</v>
+      </c>
+      <c r="I53" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J53" s="20" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="K53" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L53" s="20">
         <v>1</v>
@@ -5326,8 +5333,8 @@
       <c r="N53" s="20">
         <v>10</v>
       </c>
-      <c r="O53" s="51" t="s">
-        <v>600</v>
+      <c r="O53" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P53" s="21">
         <v>0.21609999999999999</v>
@@ -5351,23 +5358,23 @@
         <v>77</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H54" s="14"/>
-      <c r="I54" s="54" t="s">
-        <v>604</v>
+      <c r="I54" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="K54" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L54" s="14">
         <v>1</v>
@@ -5379,8 +5386,8 @@
       <c r="N54" s="14">
         <v>10</v>
       </c>
-      <c r="O54" s="51" t="s">
-        <v>600</v>
+      <c r="O54" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P54" s="15">
         <v>6.4899999999999999E-2</v>
@@ -5404,25 +5411,25 @@
         <v>78</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G55" s="20" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>405</v>
-      </c>
-      <c r="I55" s="54" t="s">
-        <v>604</v>
+        <v>401</v>
+      </c>
+      <c r="I55" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J55" s="20" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="K55" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L55" s="20">
         <v>1</v>
@@ -5434,8 +5441,8 @@
       <c r="N55" s="20">
         <v>10</v>
       </c>
-      <c r="O55" s="51" t="s">
-        <v>600</v>
+      <c r="O55" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P55" s="21">
         <v>9.7199999999999995E-2</v>
@@ -5459,25 +5466,25 @@
         <v>79</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>406</v>
-      </c>
-      <c r="I56" s="54" t="s">
-        <v>604</v>
+        <v>402</v>
+      </c>
+      <c r="I56" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="K56" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L56" s="14">
         <v>3</v>
@@ -5489,8 +5496,8 @@
       <c r="N56" s="14">
         <v>16</v>
       </c>
-      <c r="O56" s="51" t="s">
-        <v>600</v>
+      <c r="O56" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P56" s="15">
         <v>1.1589</v>
@@ -5514,25 +5521,25 @@
         <v>80</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>407</v>
-      </c>
-      <c r="I57" s="54" t="s">
-        <v>604</v>
+        <v>403</v>
+      </c>
+      <c r="I57" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J57" s="20" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="K57" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L57" s="20">
         <v>1</v>
@@ -5544,8 +5551,8 @@
       <c r="N57" s="20">
         <v>10</v>
       </c>
-      <c r="O57" s="51" t="s">
-        <v>600</v>
+      <c r="O57" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P57" s="21">
         <v>0.1066</v>
@@ -5569,25 +5576,25 @@
         <v>81</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="I58" s="54" t="s">
-        <v>604</v>
+        <v>404</v>
+      </c>
+      <c r="I58" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="K58" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L58" s="14">
         <v>1</v>
@@ -5599,8 +5606,8 @@
       <c r="N58" s="14">
         <v>10</v>
       </c>
-      <c r="O58" s="51" t="s">
-        <v>600</v>
+      <c r="O58" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P58" s="15">
         <v>0.16550000000000001</v>
@@ -5624,25 +5631,25 @@
         <v>82</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="I59" s="54" t="s">
-        <v>604</v>
+        <v>381</v>
+      </c>
+      <c r="I59" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J59" s="20" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="K59" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L59" s="20">
         <v>1</v>
@@ -5654,8 +5661,8 @@
       <c r="N59" s="20">
         <v>100</v>
       </c>
-      <c r="O59" s="51" t="s">
-        <v>600</v>
+      <c r="O59" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P59" s="21">
         <v>3.3E-3</v>
@@ -5679,25 +5686,25 @@
         <v>83</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>399</v>
-      </c>
-      <c r="I60" s="54" t="s">
-        <v>604</v>
+        <v>395</v>
+      </c>
+      <c r="I60" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="K60" s="14" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="L60" s="14">
         <v>1</v>
@@ -5709,8 +5716,8 @@
       <c r="N60" s="14">
         <v>10</v>
       </c>
-      <c r="O60" s="51" t="s">
-        <v>600</v>
+      <c r="O60" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P60" s="15">
         <v>0.2757</v>
@@ -5734,25 +5741,25 @@
         <v>84</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="I61" s="54" t="s">
-        <v>604</v>
+        <v>405</v>
+      </c>
+      <c r="I61" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J61" s="20" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="K61" s="20" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="L61" s="20">
         <v>1</v>
@@ -5764,8 +5771,8 @@
       <c r="N61" s="20">
         <v>10</v>
       </c>
-      <c r="O61" s="51" t="s">
-        <v>600</v>
+      <c r="O61" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P61" s="21">
         <v>0.13739999999999999</v>
@@ -5789,25 +5796,25 @@
         <v>85</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="I62" s="54" t="s">
-        <v>604</v>
+        <v>406</v>
+      </c>
+      <c r="I62" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L62" s="14">
         <v>4</v>
@@ -5819,8 +5826,8 @@
       <c r="N62" s="14">
         <v>40</v>
       </c>
-      <c r="O62" s="51" t="s">
-        <v>600</v>
+      <c r="O62" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P62" s="15">
         <v>2.2700000000000001E-2</v>
@@ -5844,25 +5851,25 @@
         <v>86</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="I63" s="54" t="s">
-        <v>604</v>
+        <v>406</v>
+      </c>
+      <c r="I63" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J63" s="20" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="K63" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L63" s="20">
         <v>1</v>
@@ -5874,8 +5881,8 @@
       <c r="N63" s="20">
         <v>20</v>
       </c>
-      <c r="O63" s="51" t="s">
-        <v>600</v>
+      <c r="O63" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P63" s="21">
         <v>2.3400000000000001E-2</v>
@@ -5899,25 +5906,25 @@
         <v>87</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="I64" s="54" t="s">
-        <v>604</v>
+        <v>407</v>
+      </c>
+      <c r="I64" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="K64" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L64" s="14">
         <v>1</v>
@@ -5929,8 +5936,8 @@
       <c r="N64" s="14">
         <v>50</v>
       </c>
-      <c r="O64" s="51" t="s">
-        <v>600</v>
+      <c r="O64" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P64" s="15">
         <v>1.6E-2</v>
@@ -5954,25 +5961,25 @@
         <v>88</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="I65" s="54" t="s">
-        <v>604</v>
+        <v>408</v>
+      </c>
+      <c r="I65" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J65" s="20" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="K65" s="20" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L65" s="20">
         <v>1</v>
@@ -5984,8 +5991,8 @@
       <c r="N65" s="20">
         <v>10</v>
       </c>
-      <c r="O65" s="51" t="s">
-        <v>600</v>
+      <c r="O65" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P65" s="21">
         <v>4.6199999999999998E-2</v>
@@ -6009,25 +6016,25 @@
         <v>89</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I66" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I66" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="K66" s="14" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="L66" s="14">
         <v>4</v>
@@ -6039,8 +6046,8 @@
       <c r="N66" s="14">
         <v>100</v>
       </c>
-      <c r="O66" s="51" t="s">
-        <v>600</v>
+      <c r="O66" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P66" s="15">
         <v>6.9999999999999999E-4</v>
@@ -6064,25 +6071,25 @@
         <v>90</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I67" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I67" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J67" s="20" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="K67" s="20" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="L67" s="20">
         <v>3</v>
@@ -6094,8 +6101,8 @@
       <c r="N67" s="20">
         <v>100</v>
       </c>
-      <c r="O67" s="51" t="s">
-        <v>600</v>
+      <c r="O67" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P67" s="21">
         <v>2.8E-3</v>
@@ -6119,25 +6126,25 @@
         <v>91</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H68" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I68" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I68" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="K68" s="14" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="L68" s="14">
         <v>17</v>
@@ -6149,8 +6156,8 @@
       <c r="N68" s="14">
         <v>100</v>
       </c>
-      <c r="O68" s="51" t="s">
-        <v>600</v>
+      <c r="O68" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P68" s="15">
         <v>5.0000000000000001E-4</v>
@@ -6170,51 +6177,51 @@
       <c r="C69" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D69" s="45" t="s">
+      <c r="D69" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="E69" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="F69" s="48" t="s">
-        <v>274</v>
-      </c>
-      <c r="G69" s="45" t="s">
-        <v>342</v>
+      <c r="E69" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="F69" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="G69" s="42" t="s">
+        <v>339</v>
       </c>
       <c r="H69" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I69" s="55" t="s">
-        <v>604</v>
-      </c>
-      <c r="J69" s="45" t="s">
-        <v>488</v>
-      </c>
-      <c r="K69" s="45" t="s">
-        <v>534</v>
-      </c>
-      <c r="L69" s="45">
+        <v>380</v>
+      </c>
+      <c r="I69" s="52" t="s">
+        <v>600</v>
+      </c>
+      <c r="J69" s="42" t="s">
+        <v>484</v>
+      </c>
+      <c r="K69" s="42" t="s">
+        <v>530</v>
+      </c>
+      <c r="L69" s="42">
         <v>2</v>
       </c>
-      <c r="M69" s="47">
+      <c r="M69" s="44">
         <f t="shared" ref="M69" si="60">L69*5</f>
         <v>10</v>
       </c>
-      <c r="N69" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="O69" s="47" t="s">
-        <v>600</v>
-      </c>
-      <c r="P69" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q69" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="R69" s="52" t="s">
-        <v>591</v>
+      <c r="N69" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="O69" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="P69" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q69" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="R69" s="49" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -6230,25 +6237,25 @@
         <v>93</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H70" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I70" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I70" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="L70" s="14">
         <v>2</v>
@@ -6260,8 +6267,8 @@
       <c r="N70" s="14">
         <v>100</v>
       </c>
-      <c r="O70" s="51" t="s">
-        <v>600</v>
+      <c r="O70" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P70" s="15">
         <v>1E-3</v>
@@ -6285,25 +6292,25 @@
         <v>94</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>413</v>
-      </c>
-      <c r="I71" s="54" t="s">
-        <v>604</v>
+        <v>409</v>
+      </c>
+      <c r="I71" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J71" s="20" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="K71" s="20" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="L71" s="20">
         <v>1</v>
@@ -6315,8 +6322,8 @@
       <c r="N71" s="20">
         <v>100</v>
       </c>
-      <c r="O71" s="51" t="s">
-        <v>600</v>
+      <c r="O71" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P71" s="21">
         <v>1E-3</v>
@@ -6340,25 +6347,25 @@
         <v>95</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H72" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="I72" s="54" t="s">
-        <v>604</v>
+        <v>410</v>
+      </c>
+      <c r="I72" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="K72" s="14" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="L72" s="14">
         <v>1</v>
@@ -6370,8 +6377,8 @@
       <c r="N72" s="14">
         <v>100</v>
       </c>
-      <c r="O72" s="51" t="s">
-        <v>600</v>
+      <c r="O72" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P72" s="15">
         <v>4.0000000000000002E-4</v>
@@ -6395,25 +6402,25 @@
         <v>96</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G73" s="20" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I73" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I73" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J73" s="20" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="K73" s="20" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="L73" s="20">
         <v>1</v>
@@ -6425,8 +6432,8 @@
       <c r="N73" s="20">
         <v>100</v>
       </c>
-      <c r="O73" s="51" t="s">
-        <v>600</v>
+      <c r="O73" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P73" s="21">
         <v>5.9999999999999995E-4</v>
@@ -6450,25 +6457,25 @@
         <v>97</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H74" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I74" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I74" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="K74" s="14" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="L74" s="14">
         <v>1</v>
@@ -6480,8 +6487,8 @@
       <c r="N74" s="14">
         <v>100</v>
       </c>
-      <c r="O74" s="51" t="s">
-        <v>600</v>
+      <c r="O74" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P74" s="15">
         <v>6.9999999999999999E-4</v>
@@ -6505,25 +6512,25 @@
         <v>98</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="I75" s="54" t="s">
-        <v>604</v>
+        <v>411</v>
+      </c>
+      <c r="I75" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J75" s="20" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="K75" s="20" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="L75" s="20">
         <v>1</v>
@@ -6535,8 +6542,8 @@
       <c r="N75" s="20">
         <v>100</v>
       </c>
-      <c r="O75" s="51" t="s">
-        <v>600</v>
+      <c r="O75" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P75" s="21">
         <v>6.9999999999999999E-4</v>
@@ -6560,23 +6567,23 @@
         <v>99</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H76" s="14"/>
-      <c r="I76" s="54" t="s">
-        <v>604</v>
+      <c r="I76" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="K76" s="14" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="L76" s="14">
         <v>2</v>
@@ -6588,8 +6595,8 @@
       <c r="N76" s="14">
         <v>100</v>
       </c>
-      <c r="O76" s="51" t="s">
-        <v>600</v>
+      <c r="O76" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P76" s="15">
         <v>5.9999999999999995E-4</v>
@@ -6613,25 +6620,25 @@
         <v>100</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I77" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I77" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J77" s="20" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="K77" s="20" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="L77" s="20">
         <v>2</v>
@@ -6643,8 +6650,8 @@
       <c r="N77" s="20">
         <v>100</v>
       </c>
-      <c r="O77" s="51" t="s">
-        <v>600</v>
+      <c r="O77" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P77" s="21">
         <v>5.9999999999999995E-4</v>
@@ -6668,25 +6675,25 @@
         <v>101</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="H78" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I78" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I78" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="K78" s="14" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="L78" s="14">
         <v>13</v>
@@ -6698,8 +6705,8 @@
       <c r="N78" s="14">
         <v>100</v>
       </c>
-      <c r="O78" s="51" t="s">
-        <v>600</v>
+      <c r="O78" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P78" s="15">
         <v>6.9999999999999999E-4</v>
@@ -6723,25 +6730,25 @@
         <v>102</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I79" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I79" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J79" s="20" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="K79" s="20" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="L79" s="20">
         <v>8</v>
@@ -6753,8 +6760,8 @@
       <c r="N79" s="20">
         <v>100</v>
       </c>
-      <c r="O79" s="51" t="s">
-        <v>600</v>
+      <c r="O79" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P79" s="21">
         <v>8.9999999999999998E-4</v>
@@ -6778,25 +6785,25 @@
         <v>103</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H80" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I80" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I80" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="K80" s="14" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="L80" s="14">
         <v>2</v>
@@ -6808,8 +6815,8 @@
       <c r="N80" s="14">
         <v>100</v>
       </c>
-      <c r="O80" s="51" t="s">
-        <v>600</v>
+      <c r="O80" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P80" s="15">
         <v>1E-3</v>
@@ -6833,25 +6840,25 @@
         <v>104</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I81" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I81" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J81" s="20" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="K81" s="20" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="L81" s="20">
         <v>1</v>
@@ -6863,8 +6870,8 @@
       <c r="N81" s="20">
         <v>50</v>
       </c>
-      <c r="O81" s="51" t="s">
-        <v>600</v>
+      <c r="O81" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P81" s="21">
         <v>2.0400000000000001E-2</v>
@@ -6884,51 +6891,51 @@
       <c r="C82" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D82" s="45" t="s">
+      <c r="D82" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="E82" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="F82" s="48" t="s">
-        <v>273</v>
-      </c>
-      <c r="G82" s="45" t="s">
-        <v>350</v>
+      <c r="E82" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="F82" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="G82" s="42" t="s">
+        <v>347</v>
       </c>
       <c r="H82" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I82" s="55" t="s">
-        <v>604</v>
-      </c>
-      <c r="J82" s="45" t="s">
-        <v>496</v>
-      </c>
-      <c r="K82" s="45" t="s">
-        <v>534</v>
-      </c>
-      <c r="L82" s="45">
+        <v>380</v>
+      </c>
+      <c r="I82" s="52" t="s">
+        <v>600</v>
+      </c>
+      <c r="J82" s="42" t="s">
+        <v>492</v>
+      </c>
+      <c r="K82" s="42" t="s">
+        <v>530</v>
+      </c>
+      <c r="L82" s="42">
         <v>1</v>
       </c>
-      <c r="M82" s="47">
+      <c r="M82" s="44">
         <f>L82*5</f>
         <v>5</v>
       </c>
-      <c r="N82" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="O82" s="47" t="s">
-        <v>600</v>
-      </c>
-      <c r="P82" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q82" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="R82" s="52" t="s">
-        <v>591</v>
+      <c r="N82" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="O82" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="P82" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q82" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="R82" s="49" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -6944,25 +6951,25 @@
         <v>106</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I83" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I83" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J83" s="20" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="K83" s="20" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="L83" s="20">
         <v>2</v>
@@ -6974,8 +6981,8 @@
       <c r="N83" s="20">
         <v>100</v>
       </c>
-      <c r="O83" s="51" t="s">
-        <v>600</v>
+      <c r="O83" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P83" s="21">
         <v>1E-3</v>
@@ -6999,25 +7006,25 @@
         <v>107</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H84" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I84" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I84" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="K84" s="14" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="L84" s="14">
         <v>12</v>
@@ -7029,8 +7036,8 @@
       <c r="N84" s="14">
         <v>100</v>
       </c>
-      <c r="O84" s="51" t="s">
-        <v>600</v>
+      <c r="O84" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P84" s="15">
         <v>1.1999999999999999E-3</v>
@@ -7054,25 +7061,25 @@
         <v>108</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I85" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I85" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J85" s="20" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="K85" s="20" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="L85" s="20">
         <v>2</v>
@@ -7084,8 +7091,8 @@
       <c r="N85" s="20">
         <v>100</v>
       </c>
-      <c r="O85" s="51" t="s">
-        <v>600</v>
+      <c r="O85" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P85" s="21">
         <v>1E-3</v>
@@ -7109,25 +7116,25 @@
         <v>109</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G86" s="14" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H86" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="I86" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I86" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="K86" s="14" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="L86" s="14">
         <v>1</v>
@@ -7139,8 +7146,8 @@
       <c r="N86" s="14">
         <v>100</v>
       </c>
-      <c r="O86" s="51" t="s">
-        <v>600</v>
+      <c r="O86" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P86" s="15">
         <v>5.9999999999999995E-4</v>
@@ -7164,25 +7171,25 @@
         <v>110</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I87" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I87" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J87" s="20" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="K87" s="20" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="L87" s="20">
         <v>6</v>
@@ -7194,8 +7201,8 @@
       <c r="N87" s="20">
         <v>100</v>
       </c>
-      <c r="O87" s="51" t="s">
-        <v>600</v>
+      <c r="O87" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P87" s="21">
         <v>6.9999999999999999E-4</v>
@@ -7219,25 +7226,25 @@
         <v>111</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H88" s="14" t="s">
-        <v>416</v>
-      </c>
-      <c r="I88" s="54" t="s">
-        <v>604</v>
+        <v>412</v>
+      </c>
+      <c r="I88" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="K88" s="14" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="L88" s="14">
         <v>1</v>
@@ -7249,8 +7256,8 @@
       <c r="N88" s="14">
         <v>20</v>
       </c>
-      <c r="O88" s="51" t="s">
-        <v>600</v>
+      <c r="O88" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P88" s="15">
         <v>2.07E-2</v>
@@ -7274,25 +7281,25 @@
         <v>112</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>416</v>
-      </c>
-      <c r="I89" s="54" t="s">
-        <v>604</v>
+        <v>412</v>
+      </c>
+      <c r="I89" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J89" s="20" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="K89" s="20" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="L89" s="20">
         <v>1</v>
@@ -7304,8 +7311,8 @@
       <c r="N89" s="20">
         <v>50</v>
       </c>
-      <c r="O89" s="51" t="s">
-        <v>600</v>
+      <c r="O89" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P89" s="21">
         <v>1.6799999999999999E-2</v>
@@ -7329,25 +7336,25 @@
         <v>113</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G90" s="14" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H90" s="14" t="s">
-        <v>417</v>
-      </c>
-      <c r="I90" s="54" t="s">
-        <v>604</v>
+        <v>413</v>
+      </c>
+      <c r="I90" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="K90" s="14" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="L90" s="14">
         <v>2</v>
@@ -7359,8 +7366,8 @@
       <c r="N90" s="14">
         <v>50</v>
       </c>
-      <c r="O90" s="51" t="s">
-        <v>600</v>
+      <c r="O90" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P90" s="15">
         <v>6.1999999999999998E-3</v>
@@ -7384,25 +7391,25 @@
         <v>114</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I91" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I91" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J91" s="20" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="K91" s="20" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="L91" s="20">
         <v>1</v>
@@ -7414,8 +7421,8 @@
       <c r="N91" s="20">
         <v>100</v>
       </c>
-      <c r="O91" s="51" t="s">
-        <v>600</v>
+      <c r="O91" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P91" s="21">
         <v>1.1000000000000001E-3</v>
@@ -7439,25 +7446,25 @@
         <v>115</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H92" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="I92" s="54" t="s">
-        <v>604</v>
+        <v>414</v>
+      </c>
+      <c r="I92" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="K92" s="14" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="L92" s="14">
         <v>1</v>
@@ -7469,8 +7476,8 @@
       <c r="N92" s="14">
         <v>100</v>
       </c>
-      <c r="O92" s="51" t="s">
-        <v>600</v>
+      <c r="O92" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P92" s="15">
         <v>5.0000000000000001E-4</v>
@@ -7494,25 +7501,25 @@
         <v>116</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I93" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I93" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J93" s="20" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="K93" s="20" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="L93" s="20">
         <v>1</v>
@@ -7524,8 +7531,8 @@
       <c r="N93" s="20">
         <v>20</v>
       </c>
-      <c r="O93" s="51" t="s">
-        <v>600</v>
+      <c r="O93" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P93" s="21">
         <v>2.1499999999999998E-2</v>
@@ -7549,25 +7556,25 @@
         <v>117</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G94" s="14" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H94" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="I94" s="54" t="s">
-        <v>604</v>
+        <v>415</v>
+      </c>
+      <c r="I94" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="K94" s="14" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="L94" s="14">
         <v>1</v>
@@ -7579,8 +7586,8 @@
       <c r="N94" s="14">
         <v>100</v>
       </c>
-      <c r="O94" s="51" t="s">
-        <v>600</v>
+      <c r="O94" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P94" s="15">
         <v>5.0000000000000001E-4</v>
@@ -7604,25 +7611,25 @@
         <v>118</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H95" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="I95" s="54" t="s">
-        <v>604</v>
+        <v>380</v>
+      </c>
+      <c r="I95" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J95" s="20" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="K95" s="20" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="L95" s="20">
         <v>3</v>
@@ -7634,8 +7641,8 @@
       <c r="N95" s="20">
         <v>50</v>
       </c>
-      <c r="O95" s="51" t="s">
-        <v>600</v>
+      <c r="O95" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P95" s="21">
         <v>8.2000000000000007E-3</v>
@@ -7659,25 +7666,25 @@
         <v>119</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F96" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H96" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="I96" s="54" t="s">
-        <v>604</v>
+        <v>416</v>
+      </c>
+      <c r="I96" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="K96" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L96" s="14">
         <v>3</v>
@@ -7689,8 +7696,8 @@
       <c r="N96" s="14">
         <v>20</v>
       </c>
-      <c r="O96" s="51" t="s">
-        <v>600</v>
+      <c r="O96" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P96" s="15">
         <v>0.1552</v>
@@ -7714,25 +7721,25 @@
         <v>120</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G97" s="20" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>421</v>
-      </c>
-      <c r="I97" s="54" t="s">
-        <v>604</v>
+        <v>417</v>
+      </c>
+      <c r="I97" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J97" s="20" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="K97" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L97" s="20">
         <v>4</v>
@@ -7744,8 +7751,8 @@
       <c r="N97" s="20">
         <v>21</v>
       </c>
-      <c r="O97" s="51" t="s">
-        <v>600</v>
+      <c r="O97" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P97" s="21">
         <v>0.5262</v>
@@ -7769,25 +7776,25 @@
         <v>121</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H98" s="14" t="s">
-        <v>422</v>
-      </c>
-      <c r="I98" s="54" t="s">
-        <v>604</v>
+        <v>418</v>
+      </c>
+      <c r="I98" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="K98" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L98" s="14">
         <v>1</v>
@@ -7799,8 +7806,8 @@
       <c r="N98" s="14">
         <v>6</v>
       </c>
-      <c r="O98" s="51" t="s">
-        <v>600</v>
+      <c r="O98" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P98" s="15">
         <v>6.5850999999999997</v>
@@ -7824,25 +7831,25 @@
         <v>122</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F99" s="20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>423</v>
-      </c>
-      <c r="I99" s="54" t="s">
-        <v>604</v>
+        <v>419</v>
+      </c>
+      <c r="I99" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J99" s="20" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="K99" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L99" s="20">
         <v>1</v>
@@ -7854,8 +7861,8 @@
       <c r="N99" s="20">
         <v>6</v>
       </c>
-      <c r="O99" s="51" t="s">
-        <v>600</v>
+      <c r="O99" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P99" s="21">
         <v>2.6966000000000001</v>
@@ -7879,25 +7886,25 @@
         <v>123</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F100" s="14" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G100" s="14" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H100" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="I100" s="54" t="s">
-        <v>604</v>
+        <v>420</v>
+      </c>
+      <c r="I100" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="K100" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L100" s="14">
         <v>1</v>
@@ -7909,8 +7916,8 @@
       <c r="N100" s="14">
         <v>6</v>
       </c>
-      <c r="O100" s="51" t="s">
-        <v>600</v>
+      <c r="O100" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P100" s="15">
         <v>1.5093000000000001</v>
@@ -7934,25 +7941,25 @@
         <v>124</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F101" s="20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>425</v>
-      </c>
-      <c r="I101" s="54" t="s">
-        <v>604</v>
+        <v>421</v>
+      </c>
+      <c r="I101" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J101" s="20" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="K101" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L101" s="20">
         <v>1</v>
@@ -7964,8 +7971,8 @@
       <c r="N101" s="20">
         <v>10</v>
       </c>
-      <c r="O101" s="51" t="s">
-        <v>600</v>
+      <c r="O101" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P101" s="21">
         <v>0.28899999999999998</v>
@@ -7989,25 +7996,25 @@
         <v>125</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G102" s="14" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H102" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="I102" s="54" t="s">
-        <v>604</v>
+        <v>420</v>
+      </c>
+      <c r="I102" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J102" s="14" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="K102" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L102" s="14">
         <v>1</v>
@@ -8019,8 +8026,8 @@
       <c r="N102" s="14">
         <v>6</v>
       </c>
-      <c r="O102" s="51" t="s">
-        <v>600</v>
+      <c r="O102" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P102" s="15">
         <v>2.9133</v>
@@ -8044,25 +8051,25 @@
         <v>126</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F103" s="20" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="I103" s="54" t="s">
-        <v>604</v>
+        <v>422</v>
+      </c>
+      <c r="I103" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J103" s="20" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="K103" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L103" s="20">
         <v>1</v>
@@ -8074,8 +8081,8 @@
       <c r="N103" s="20">
         <v>10</v>
       </c>
-      <c r="O103" s="51" t="s">
-        <v>600</v>
+      <c r="O103" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P103" s="21">
         <v>0.1474</v>
@@ -8099,25 +8106,25 @@
         <v>127</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G104" s="14" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H104" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="I104" s="54" t="s">
-        <v>604</v>
+        <v>420</v>
+      </c>
+      <c r="I104" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J104" s="14" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="K104" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L104" s="14">
         <v>2</v>
@@ -8129,8 +8136,8 @@
       <c r="N104" s="14">
         <v>11</v>
       </c>
-      <c r="O104" s="51" t="s">
-        <v>600</v>
+      <c r="O104" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P104" s="15">
         <v>2.984</v>
@@ -8154,25 +8161,25 @@
         <v>128</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F105" s="20" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>427</v>
-      </c>
-      <c r="I105" s="54" t="s">
-        <v>604</v>
+        <v>423</v>
+      </c>
+      <c r="I105" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J105" s="20" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="K105" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L105" s="20">
         <v>1</v>
@@ -8184,8 +8191,8 @@
       <c r="N105" s="20">
         <v>6</v>
       </c>
-      <c r="O105" s="51" t="s">
-        <v>600</v>
+      <c r="O105" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P105" s="21">
         <v>0.33610000000000001</v>
@@ -8209,25 +8216,25 @@
         <v>129</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G106" s="14" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H106" s="14" t="s">
-        <v>428</v>
-      </c>
-      <c r="I106" s="54" t="s">
-        <v>604</v>
+        <v>424</v>
+      </c>
+      <c r="I106" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="K106" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L106" s="14">
         <v>1</v>
@@ -8239,8 +8246,8 @@
       <c r="N106" s="14">
         <v>6</v>
       </c>
-      <c r="O106" s="51" t="s">
-        <v>600</v>
+      <c r="O106" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P106" s="15">
         <v>8.6266999999999996</v>
@@ -8264,25 +8271,25 @@
         <v>130</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F107" s="20" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>429</v>
-      </c>
-      <c r="I107" s="54" t="s">
-        <v>604</v>
+        <v>425</v>
+      </c>
+      <c r="I107" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J107" s="20" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="K107" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L107" s="20">
         <v>1</v>
@@ -8294,8 +8301,8 @@
       <c r="N107" s="20">
         <v>6</v>
       </c>
-      <c r="O107" s="51" t="s">
-        <v>600</v>
+      <c r="O107" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P107" s="21">
         <v>2.6192000000000002</v>
@@ -8319,25 +8326,25 @@
         <v>131</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G108" s="14" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H108" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="I108" s="54" t="s">
-        <v>604</v>
+        <v>426</v>
+      </c>
+      <c r="I108" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J108" s="14" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="K108" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L108" s="14">
         <v>1</v>
@@ -8349,8 +8356,8 @@
       <c r="N108" s="14">
         <v>10</v>
       </c>
-      <c r="O108" s="51" t="s">
-        <v>600</v>
+      <c r="O108" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P108" s="15">
         <v>0.28999999999999998</v>
@@ -8374,25 +8381,25 @@
         <v>132</v>
       </c>
       <c r="E109" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F109" s="20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>424</v>
-      </c>
-      <c r="I109" s="54" t="s">
-        <v>604</v>
+        <v>420</v>
+      </c>
+      <c r="I109" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J109" s="20" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="K109" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L109" s="20">
         <v>1</v>
@@ -8404,8 +8411,8 @@
       <c r="N109" s="20">
         <v>6</v>
       </c>
-      <c r="O109" s="51" t="s">
-        <v>600</v>
+      <c r="O109" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P109" s="21">
         <v>0.3483</v>
@@ -8425,51 +8432,51 @@
       <c r="C110" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D110" s="45" t="s">
+      <c r="D110" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="E110" s="46" t="s">
-        <v>237</v>
-      </c>
-      <c r="F110" s="48" t="s">
-        <v>290</v>
-      </c>
-      <c r="G110" s="47" t="s">
-        <v>379</v>
-      </c>
-      <c r="H110" s="47" t="s">
-        <v>431</v>
-      </c>
-      <c r="I110" s="55" t="s">
-        <v>604</v>
-      </c>
-      <c r="J110" s="47" t="s">
-        <v>525</v>
-      </c>
-      <c r="K110" s="47" t="s">
-        <v>534</v>
-      </c>
-      <c r="L110" s="47">
+      <c r="E110" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="F110" s="45" t="s">
+        <v>288</v>
+      </c>
+      <c r="G110" s="44" t="s">
+        <v>376</v>
+      </c>
+      <c r="H110" s="44" t="s">
+        <v>427</v>
+      </c>
+      <c r="I110" s="52" t="s">
+        <v>600</v>
+      </c>
+      <c r="J110" s="44" t="s">
+        <v>521</v>
+      </c>
+      <c r="K110" s="44" t="s">
+        <v>530</v>
+      </c>
+      <c r="L110" s="44">
         <v>1</v>
       </c>
-      <c r="M110" s="47">
+      <c r="M110" s="44">
         <f>L110*5</f>
         <v>5</v>
       </c>
-      <c r="N110" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="O110" s="47" t="s">
-        <v>600</v>
-      </c>
-      <c r="P110" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q110" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="R110" s="52" t="s">
-        <v>591</v>
+      <c r="N110" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="O110" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="P110" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q110" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="R110" s="49" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="111" spans="1:18" ht="24" x14ac:dyDescent="0.25">
@@ -8485,25 +8492,25 @@
         <v>134</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>432</v>
-      </c>
-      <c r="I111" s="54" t="s">
-        <v>604</v>
+        <v>428</v>
+      </c>
+      <c r="I111" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J111" s="20" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="K111" s="20" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="L111" s="20">
         <v>1</v>
@@ -8515,8 +8522,8 @@
       <c r="N111" s="20">
         <v>10</v>
       </c>
-      <c r="O111" s="51" t="s">
-        <v>600</v>
+      <c r="O111" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P111" s="21">
         <v>0.30080000000000001</v>
@@ -8540,25 +8547,25 @@
         <v>135</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G112" s="14" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="H112" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="I112" s="54" t="s">
-        <v>604</v>
+        <v>429</v>
+      </c>
+      <c r="I112" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="K112" s="14" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="L112" s="14">
         <v>1</v>
@@ -8570,8 +8577,8 @@
       <c r="N112" s="14">
         <v>10</v>
       </c>
-      <c r="O112" s="51" t="s">
-        <v>600</v>
+      <c r="O112" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P112" s="15">
         <v>6.5600000000000006E-2</v>
@@ -8595,25 +8602,25 @@
         <v>136</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F113" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>431</v>
-      </c>
-      <c r="I113" s="54" t="s">
-        <v>604</v>
+        <v>427</v>
+      </c>
+      <c r="I113" s="51" t="s">
+        <v>600</v>
       </c>
       <c r="J113" s="20" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="K113" s="20" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="L113" s="20">
         <v>1</v>
@@ -8625,8 +8632,8 @@
       <c r="N113" s="20">
         <v>10</v>
       </c>
-      <c r="O113" s="51" t="s">
-        <v>600</v>
+      <c r="O113" s="48" t="s">
+        <v>596</v>
       </c>
       <c r="P113" s="21">
         <v>0.25950000000000001</v>
@@ -8651,14 +8658,14 @@
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
       <c r="M114" s="1"/>
-      <c r="N114" s="43" t="s">
+      <c r="N114" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="O114" s="44"/>
-      <c r="P114" s="44"/>
+      <c r="O114" s="55"/>
+      <c r="P114" s="55"/>
       <c r="Q114" s="18">
         <f>SUM(Q8:Q113)</f>
-        <v>311.78460000000001</v>
+        <v>312.26459999999992</v>
       </c>
       <c r="R114" s="1"/>
     </row>
@@ -8676,14 +8683,14 @@
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
       <c r="M115" s="1"/>
-      <c r="N115" s="43" t="s">
+      <c r="N115" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="O115" s="44"/>
-      <c r="P115" s="44"/>
+      <c r="O115" s="55"/>
+      <c r="P115" s="55"/>
       <c r="Q115" s="19">
         <f>Q114/5</f>
-        <v>62.356920000000002</v>
+        <v>62.452919999999985</v>
       </c>
       <c r="R115" s="1"/>
     </row>
@@ -8797,8 +8804,9 @@
     <hyperlink ref="O112" r:id="rId98"/>
     <hyperlink ref="O113" r:id="rId99"/>
     <hyperlink ref="O49" r:id="rId100"/>
+    <hyperlink ref="O36" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId101"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId102"/>
 </worksheet>
 </file>
--- a/Design Files/Control-Board-v1.0/BOM/eSpark-BOM-Control-Board-v1.0.xlsx
+++ b/Design Files/Control-Board-v1.0/BOM/eSpark-BOM-Control-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="675">
   <si>
     <t>Component list</t>
   </si>
@@ -1993,6 +1993,57 @@
   </si>
   <si>
     <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Jumper</t>
+  </si>
+  <si>
+    <t>P=2.54mm Shunts, Jumpers ROHS</t>
+  </si>
+  <si>
+    <t>X2541-A1NIB</t>
+  </si>
+  <si>
+    <t>Ethernet Cable</t>
+  </si>
+  <si>
+    <t>Cat6 Gigabit Ethernet Cable 1m Cable/ModularCable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGREEN </t>
+  </si>
+  <si>
+    <t>32V 1kA Blade fuse 2A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>0287002.PXCN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Littelfuse </t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>SSD1315 I2C 128x64 0.96 OLED Display ROHS</t>
+  </si>
+  <si>
+    <t>HS96L03W2C03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS </t>
+  </si>
+  <si>
+    <t>C5248080</t>
+  </si>
+  <si>
+    <t>C142680</t>
+  </si>
+  <si>
+    <t>C2938578</t>
+  </si>
+  <si>
+    <t>C3015021</t>
   </si>
 </sst>
 </file>
@@ -2375,7 +2426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2508,9 +2559,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2520,6 +2568,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="15" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2536,12 +2590,6 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2831,7 +2879,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R138"/>
+  <dimension ref="A1:R142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="10" bestFit="1" customWidth="1"/>
@@ -2847,7 +2895,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -2864,14 +2912,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -3059,7 +3107,7 @@
       <c r="H8" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I8" s="60" t="s">
+      <c r="I8" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J8" s="14" t="s">
@@ -3093,7 +3141,7 @@
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B124" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B128" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -3114,7 +3162,7 @@
       <c r="H9" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I9" s="60" t="s">
+      <c r="I9" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J9" s="20" t="s">
@@ -3169,7 +3217,7 @@
       <c r="H10" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I10" s="60" t="s">
+      <c r="I10" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J10" s="14" t="s">
@@ -3224,7 +3272,7 @@
       <c r="H11" s="42" t="s">
         <v>425</v>
       </c>
-      <c r="I11" s="61" t="s">
+      <c r="I11" s="56" t="s">
         <v>653</v>
       </c>
       <c r="J11" s="42" t="s">
@@ -3280,7 +3328,7 @@
       <c r="H12" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I12" s="60" t="s">
+      <c r="I12" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J12" s="14" t="s">
@@ -3296,16 +3344,16 @@
         <f>L12*5</f>
         <v>20</v>
       </c>
-      <c r="N12" s="53">
+      <c r="N12" s="52">
         <v>100</v>
       </c>
-      <c r="O12" s="52" t="s">
-        <v>640</v>
-      </c>
-      <c r="P12" s="54">
+      <c r="O12" s="51" t="s">
+        <v>640</v>
+      </c>
+      <c r="P12" s="53">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="Q12" s="55">
+      <c r="Q12" s="54">
         <f>P12*N12</f>
         <v>0.21</v>
       </c>
@@ -3335,7 +3383,7 @@
       <c r="H13" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I13" s="60" t="s">
+      <c r="I13" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J13" s="20" t="s">
@@ -3360,7 +3408,7 @@
       <c r="P13" s="21">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="Q13" s="55">
+      <c r="Q13" s="54">
         <f t="shared" ref="Q13:Q76" si="5">P13*N13</f>
         <v>0.87500000000000011</v>
       </c>
@@ -3390,7 +3438,7 @@
       <c r="H14" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="I14" s="60" t="s">
+      <c r="I14" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J14" s="14" t="s">
@@ -3415,7 +3463,7 @@
       <c r="P14" s="15">
         <v>1.32E-2</v>
       </c>
-      <c r="Q14" s="55">
+      <c r="Q14" s="54">
         <f t="shared" si="5"/>
         <v>1.5840000000000001</v>
       </c>
@@ -3445,7 +3493,7 @@
       <c r="H15" s="20" t="s">
         <v>426</v>
       </c>
-      <c r="I15" s="60" t="s">
+      <c r="I15" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J15" s="20" t="s">
@@ -3470,7 +3518,7 @@
       <c r="P15" s="15">
         <v>9.4500000000000001E-2</v>
       </c>
-      <c r="Q15" s="55">
+      <c r="Q15" s="54">
         <f t="shared" si="5"/>
         <v>4.2525000000000004</v>
       </c>
@@ -3498,7 +3546,7 @@
       <c r="H16" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="I16" s="60" t="s">
+      <c r="I16" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J16" s="14" t="s">
@@ -3521,7 +3569,7 @@
         <v>640</v>
       </c>
       <c r="P16" s="15"/>
-      <c r="Q16" s="55">
+      <c r="Q16" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3551,7 +3599,7 @@
       <c r="H17" s="20" t="s">
         <v>428</v>
       </c>
-      <c r="I17" s="60" t="s">
+      <c r="I17" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J17" s="20" t="s">
@@ -3576,7 +3624,7 @@
       <c r="P17" s="15">
         <v>0.29310000000000003</v>
       </c>
-      <c r="Q17" s="55">
+      <c r="Q17" s="54">
         <f t="shared" si="5"/>
         <v>5.8620000000000001</v>
       </c>
@@ -3606,7 +3654,7 @@
       <c r="H18" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I18" s="60" t="s">
+      <c r="I18" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J18" s="14" t="s">
@@ -3625,13 +3673,13 @@
       <c r="N18" s="14">
         <v>20</v>
       </c>
-      <c r="O18" s="52" t="s">
+      <c r="O18" s="51" t="s">
         <v>640</v>
       </c>
       <c r="P18" s="15">
         <v>3.7199999999999997E-2</v>
       </c>
-      <c r="Q18" s="55">
+      <c r="Q18" s="54">
         <f t="shared" si="5"/>
         <v>0.74399999999999999</v>
       </c>
@@ -3661,7 +3709,7 @@
       <c r="H19" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I19" s="60" t="s">
+      <c r="I19" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J19" s="20" t="s">
@@ -3680,13 +3728,13 @@
       <c r="N19" s="20">
         <v>10</v>
       </c>
-      <c r="O19" s="52" t="s">
+      <c r="O19" s="51" t="s">
         <v>640</v>
       </c>
       <c r="P19" s="21">
         <v>8.6099999999999996E-2</v>
       </c>
-      <c r="Q19" s="55">
+      <c r="Q19" s="54">
         <f t="shared" si="5"/>
         <v>0.86099999999999999</v>
       </c>
@@ -3716,7 +3764,7 @@
       <c r="H20" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I20" s="60" t="s">
+      <c r="I20" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J20" s="14" t="s">
@@ -3741,7 +3789,7 @@
       <c r="P20" s="15">
         <v>6.83E-2</v>
       </c>
-      <c r="Q20" s="55">
+      <c r="Q20" s="54">
         <f t="shared" si="5"/>
         <v>1.3660000000000001</v>
       </c>
@@ -3771,7 +3819,7 @@
       <c r="H21" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I21" s="60" t="s">
+      <c r="I21" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J21" s="14" t="s">
@@ -3796,7 +3844,7 @@
       <c r="P21" s="15">
         <v>1E-3</v>
       </c>
-      <c r="Q21" s="55">
+      <c r="Q21" s="54">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
@@ -3826,7 +3874,7 @@
       <c r="H22" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="I22" s="60" t="s">
+      <c r="I22" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J22" s="14" t="s">
@@ -3851,7 +3899,7 @@
       <c r="P22" s="21">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="Q22" s="55">
+      <c r="Q22" s="54">
         <f t="shared" si="5"/>
         <v>0.42</v>
       </c>
@@ -3881,7 +3929,7 @@
       <c r="H23" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I23" s="60" t="s">
+      <c r="I23" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -3900,13 +3948,13 @@
       <c r="N23" s="20">
         <v>100</v>
       </c>
-      <c r="O23" s="52" t="s">
+      <c r="O23" s="51" t="s">
         <v>640</v>
       </c>
       <c r="P23" s="21">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="Q23" s="55">
+      <c r="Q23" s="54">
         <f t="shared" si="5"/>
         <v>0.38999999999999996</v>
       </c>
@@ -3936,7 +3984,7 @@
       <c r="H24" s="14" t="s">
         <v>429</v>
       </c>
-      <c r="I24" s="60" t="s">
+      <c r="I24" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J24" s="14" t="s">
@@ -3955,13 +4003,13 @@
       <c r="N24" s="14">
         <v>100</v>
       </c>
-      <c r="O24" s="52" t="s">
+      <c r="O24" s="51" t="s">
         <v>640</v>
       </c>
       <c r="P24" s="15">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="Q24" s="55">
+      <c r="Q24" s="54">
         <f t="shared" si="5"/>
         <v>0.38999999999999996</v>
       </c>
@@ -3991,7 +4039,7 @@
       <c r="H25" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="I25" s="60" t="s">
+      <c r="I25" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -4016,7 +4064,7 @@
       <c r="P25" s="15">
         <v>2.8E-3</v>
       </c>
-      <c r="Q25" s="55">
+      <c r="Q25" s="54">
         <f t="shared" si="5"/>
         <v>0.27999999999999997</v>
       </c>
@@ -4046,7 +4094,7 @@
       <c r="H26" s="14" t="s">
         <v>430</v>
       </c>
-      <c r="I26" s="60" t="s">
+      <c r="I26" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J26" s="14" t="s">
@@ -4071,7 +4119,7 @@
       <c r="P26" s="21">
         <v>1.4E-2</v>
       </c>
-      <c r="Q26" s="55">
+      <c r="Q26" s="54">
         <f t="shared" si="5"/>
         <v>0.70000000000000007</v>
       </c>
@@ -4101,7 +4149,7 @@
       <c r="H27" s="20" t="s">
         <v>431</v>
       </c>
-      <c r="I27" s="60" t="s">
+      <c r="I27" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J27" s="20" t="s">
@@ -4126,7 +4174,7 @@
       <c r="P27" s="15">
         <v>2.8E-3</v>
       </c>
-      <c r="Q27" s="55">
+      <c r="Q27" s="54">
         <f t="shared" si="5"/>
         <v>0.27999999999999997</v>
       </c>
@@ -4156,7 +4204,7 @@
       <c r="H28" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I28" s="60" t="s">
+      <c r="I28" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J28" s="14" t="s">
@@ -4181,7 +4229,7 @@
       <c r="P28" s="21">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="Q28" s="55">
+      <c r="Q28" s="54">
         <f t="shared" si="5"/>
         <v>0.26</v>
       </c>
@@ -4211,7 +4259,7 @@
       <c r="H29" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I29" s="60" t="s">
+      <c r="I29" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J29" s="20" t="s">
@@ -4236,7 +4284,7 @@
       <c r="P29" s="15">
         <v>2.8E-3</v>
       </c>
-      <c r="Q29" s="55">
+      <c r="Q29" s="54">
         <f t="shared" si="5"/>
         <v>0.27999999999999997</v>
       </c>
@@ -4266,7 +4314,7 @@
       <c r="H30" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I30" s="60" t="s">
+      <c r="I30" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J30" s="14" t="s">
@@ -4291,7 +4339,7 @@
       <c r="P30" s="21">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="Q30" s="55">
+      <c r="Q30" s="54">
         <f t="shared" si="5"/>
         <v>0.26</v>
       </c>
@@ -4321,7 +4369,7 @@
       <c r="H31" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I31" s="60" t="s">
+      <c r="I31" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J31" s="20" t="s">
@@ -4346,7 +4394,7 @@
       <c r="P31" s="15">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="Q31" s="55">
+      <c r="Q31" s="54">
         <f t="shared" si="5"/>
         <v>0.59500000000000008</v>
       </c>
@@ -4376,7 +4424,7 @@
       <c r="H32" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I32" s="60" t="s">
+      <c r="I32" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J32" s="14" t="s">
@@ -4401,7 +4449,7 @@
       <c r="P32" s="21">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="Q32" s="55">
+      <c r="Q32" s="54">
         <f t="shared" si="5"/>
         <v>0.31</v>
       </c>
@@ -4431,7 +4479,7 @@
       <c r="H33" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="I33" s="60" t="s">
+      <c r="I33" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J33" s="20" t="s">
@@ -4456,7 +4504,7 @@
       <c r="P33" s="21">
         <v>0.10249999999999999</v>
       </c>
-      <c r="Q33" s="55">
+      <c r="Q33" s="54">
         <f t="shared" si="5"/>
         <v>2.5625</v>
       </c>
@@ -4486,7 +4534,7 @@
       <c r="H34" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="I34" s="60" t="s">
+      <c r="I34" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J34" s="14" t="s">
@@ -4511,7 +4559,7 @@
       <c r="P34" s="21">
         <v>2.4E-2</v>
       </c>
-      <c r="Q34" s="55">
+      <c r="Q34" s="54">
         <f t="shared" si="5"/>
         <v>0.48</v>
       </c>
@@ -4541,7 +4589,7 @@
       <c r="H35" s="20" t="s">
         <v>434</v>
       </c>
-      <c r="I35" s="60" t="s">
+      <c r="I35" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J35" s="20" t="s">
@@ -4566,7 +4614,7 @@
       <c r="P35" s="21">
         <v>1.29E-2</v>
       </c>
-      <c r="Q35" s="55">
+      <c r="Q35" s="54">
         <f t="shared" si="5"/>
         <v>1.29</v>
       </c>
@@ -4596,7 +4644,7 @@
       <c r="H36" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="I36" s="60" t="s">
+      <c r="I36" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J36" s="14" t="s">
@@ -4621,7 +4669,7 @@
       <c r="P36" s="15">
         <v>4.53E-2</v>
       </c>
-      <c r="Q36" s="55">
+      <c r="Q36" s="54">
         <f t="shared" si="5"/>
         <v>0.45300000000000001</v>
       </c>
@@ -4651,7 +4699,7 @@
       <c r="H37" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="I37" s="60" t="s">
+      <c r="I37" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J37" s="20" t="s">
@@ -4676,7 +4724,7 @@
       <c r="P37" s="21">
         <v>0.153</v>
       </c>
-      <c r="Q37" s="55">
+      <c r="Q37" s="54">
         <f t="shared" si="5"/>
         <v>1.53</v>
       </c>
@@ -4706,7 +4754,7 @@
       <c r="H38" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="I38" s="60" t="s">
+      <c r="I38" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J38" s="14" t="s">
@@ -4731,7 +4779,7 @@
       <c r="P38" s="15">
         <v>3.0800000000000001E-2</v>
       </c>
-      <c r="Q38" s="55">
+      <c r="Q38" s="54">
         <f t="shared" si="5"/>
         <v>0.61599999999999999</v>
       </c>
@@ -4761,7 +4809,7 @@
       <c r="H39" s="20" t="s">
         <v>437</v>
       </c>
-      <c r="I39" s="60" t="s">
+      <c r="I39" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J39" s="20" t="s">
@@ -4780,13 +4828,13 @@
       <c r="N39" s="20">
         <v>15</v>
       </c>
-      <c r="O39" s="52" t="s">
+      <c r="O39" s="51" t="s">
         <v>640</v>
       </c>
       <c r="P39" s="21">
         <v>0.1729</v>
       </c>
-      <c r="Q39" s="55">
+      <c r="Q39" s="54">
         <f t="shared" si="5"/>
         <v>2.5935000000000001</v>
       </c>
@@ -4816,7 +4864,7 @@
       <c r="H40" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="I40" s="60" t="s">
+      <c r="I40" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J40" s="14" t="s">
@@ -4835,13 +4883,13 @@
       <c r="N40" s="14">
         <v>20</v>
       </c>
-      <c r="O40" s="52" t="s">
+      <c r="O40" s="51" t="s">
         <v>640</v>
       </c>
       <c r="P40" s="15">
         <v>3.5200000000000002E-2</v>
       </c>
-      <c r="Q40" s="55">
+      <c r="Q40" s="54">
         <f t="shared" si="5"/>
         <v>0.70400000000000007</v>
       </c>
@@ -4871,7 +4919,7 @@
       <c r="H41" s="20" t="s">
         <v>439</v>
       </c>
-      <c r="I41" s="60" t="s">
+      <c r="I41" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J41" s="20" t="s">
@@ -4890,13 +4938,13 @@
       <c r="N41" s="20">
         <v>25</v>
       </c>
-      <c r="O41" s="52" t="s">
+      <c r="O41" s="51" t="s">
         <v>640</v>
       </c>
       <c r="P41" s="21">
         <v>0.1081</v>
       </c>
-      <c r="Q41" s="55">
+      <c r="Q41" s="54">
         <f t="shared" si="5"/>
         <v>2.7025000000000001</v>
       </c>
@@ -4926,7 +4974,7 @@
       <c r="H42" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="I42" s="60" t="s">
+      <c r="I42" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J42" s="14" t="s">
@@ -4945,13 +4993,13 @@
       <c r="N42" s="14">
         <v>50</v>
       </c>
-      <c r="O42" s="52" t="s">
+      <c r="O42" s="51" t="s">
         <v>640</v>
       </c>
       <c r="P42" s="15">
         <v>5.8900000000000001E-2</v>
       </c>
-      <c r="Q42" s="55">
+      <c r="Q42" s="54">
         <f t="shared" si="5"/>
         <v>2.9449999999999998</v>
       </c>
@@ -4981,7 +5029,7 @@
       <c r="H43" s="20" t="s">
         <v>440</v>
       </c>
-      <c r="I43" s="60" t="s">
+      <c r="I43" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J43" s="20" t="s">
@@ -5006,7 +5054,7 @@
       <c r="P43" s="15">
         <v>5.5500000000000001E-2</v>
       </c>
-      <c r="Q43" s="55">
+      <c r="Q43" s="54">
         <f t="shared" si="5"/>
         <v>2.7749999999999999</v>
       </c>
@@ -5036,7 +5084,7 @@
       <c r="H44" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="I44" s="60" t="s">
+      <c r="I44" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J44" s="14" t="s">
@@ -5061,7 +5109,7 @@
       <c r="P44" s="21">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="Q44" s="55">
+      <c r="Q44" s="54">
         <f t="shared" si="5"/>
         <v>0.35000000000000003</v>
       </c>
@@ -5091,7 +5139,7 @@
       <c r="H45" s="20" t="s">
         <v>441</v>
       </c>
-      <c r="I45" s="60" t="s">
+      <c r="I45" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J45" s="20" t="s">
@@ -5116,7 +5164,7 @@
       <c r="P45" s="15">
         <v>1.52E-2</v>
       </c>
-      <c r="Q45" s="55">
+      <c r="Q45" s="54">
         <f t="shared" si="5"/>
         <v>0.76</v>
       </c>
@@ -5146,7 +5194,7 @@
       <c r="H46" s="14" t="s">
         <v>442</v>
       </c>
-      <c r="I46" s="60" t="s">
+      <c r="I46" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J46" s="14" t="s">
@@ -5171,7 +5219,7 @@
       <c r="P46" s="21">
         <v>0.1482</v>
       </c>
-      <c r="Q46" s="55">
+      <c r="Q46" s="54">
         <f t="shared" si="5"/>
         <v>2.2229999999999999</v>
       </c>
@@ -5201,7 +5249,7 @@
       <c r="H47" s="20" t="s">
         <v>443</v>
       </c>
-      <c r="I47" s="60" t="s">
+      <c r="I47" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J47" s="20" t="s">
@@ -5226,7 +5274,7 @@
       <c r="P47" s="15">
         <v>1.6899999999999998E-2</v>
       </c>
-      <c r="Q47" s="55">
+      <c r="Q47" s="54">
         <f t="shared" si="5"/>
         <v>0.84499999999999997</v>
       </c>
@@ -5256,7 +5304,7 @@
       <c r="H48" s="14" t="s">
         <v>444</v>
       </c>
-      <c r="I48" s="60" t="s">
+      <c r="I48" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J48" s="14" t="s">
@@ -5281,7 +5329,7 @@
       <c r="P48" s="21">
         <v>6.4100000000000004E-2</v>
       </c>
-      <c r="Q48" s="55">
+      <c r="Q48" s="54">
         <f t="shared" si="5"/>
         <v>0.76920000000000011</v>
       </c>
@@ -5311,7 +5359,7 @@
       <c r="H49" s="20" t="s">
         <v>445</v>
       </c>
-      <c r="I49" s="60" t="s">
+      <c r="I49" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J49" s="20" t="s">
@@ -5336,7 +5384,7 @@
       <c r="P49" s="21">
         <v>0.1089</v>
       </c>
-      <c r="Q49" s="55">
+      <c r="Q49" s="54">
         <f t="shared" si="5"/>
         <v>1.089</v>
       </c>
@@ -5391,7 +5439,7 @@
       <c r="P50" s="15">
         <v>1.4500000000000001E-2</v>
       </c>
-      <c r="Q50" s="55">
+      <c r="Q50" s="54">
         <f t="shared" si="5"/>
         <v>0.72500000000000009</v>
       </c>
@@ -5421,7 +5469,7 @@
       <c r="H51" s="20" t="s">
         <v>445</v>
       </c>
-      <c r="I51" s="60" t="s">
+      <c r="I51" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J51" s="20" t="s">
@@ -5446,7 +5494,7 @@
       <c r="P51" s="21">
         <v>6.5199999999999994E-2</v>
       </c>
-      <c r="Q51" s="55">
+      <c r="Q51" s="54">
         <f t="shared" si="5"/>
         <v>0.65199999999999991</v>
       </c>
@@ -5476,7 +5524,7 @@
       <c r="H52" s="14" t="s">
         <v>445</v>
       </c>
-      <c r="I52" s="60" t="s">
+      <c r="I52" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J52" s="14" t="s">
@@ -5501,7 +5549,7 @@
       <c r="P52" s="15">
         <v>5.1299999999999998E-2</v>
       </c>
-      <c r="Q52" s="55">
+      <c r="Q52" s="54">
         <f t="shared" si="5"/>
         <v>1.026</v>
       </c>
@@ -5531,7 +5579,7 @@
       <c r="H53" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="I53" s="60" t="s">
+      <c r="I53" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J53" s="20" t="s">
@@ -5556,7 +5604,7 @@
       <c r="P53" s="21">
         <v>4.2200000000000001E-2</v>
       </c>
-      <c r="Q53" s="55">
+      <c r="Q53" s="54">
         <f t="shared" si="5"/>
         <v>0.42200000000000004</v>
       </c>
@@ -5586,7 +5634,7 @@
       <c r="H54" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="I54" s="60" t="s">
+      <c r="I54" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J54" s="14" t="s">
@@ -5611,7 +5659,7 @@
       <c r="P54" s="15">
         <v>1.3324</v>
       </c>
-      <c r="Q54" s="55">
+      <c r="Q54" s="54">
         <f t="shared" si="5"/>
         <v>7.9944000000000006</v>
       </c>
@@ -5641,7 +5689,7 @@
       <c r="H55" s="20" t="s">
         <v>448</v>
       </c>
-      <c r="I55" s="60" t="s">
+      <c r="I55" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J55" s="14" t="s">
@@ -5666,7 +5714,7 @@
       <c r="P55" s="15">
         <v>0.30509999999999998</v>
       </c>
-      <c r="Q55" s="55">
+      <c r="Q55" s="54">
         <f t="shared" si="5"/>
         <v>1.8306</v>
       </c>
@@ -5696,7 +5744,7 @@
       <c r="H56" s="14" t="s">
         <v>445</v>
       </c>
-      <c r="I56" s="60" t="s">
+      <c r="I56" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J56" s="14" t="s">
@@ -5721,7 +5769,7 @@
       <c r="P56" s="15">
         <v>2.7199999999999998E-2</v>
       </c>
-      <c r="Q56" s="55">
+      <c r="Q56" s="54">
         <f t="shared" si="5"/>
         <v>1.0879999999999999</v>
       </c>
@@ -5751,7 +5799,7 @@
       <c r="H57" s="20" t="s">
         <v>449</v>
       </c>
-      <c r="I57" s="60" t="s">
+      <c r="I57" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J57" s="20" t="s">
@@ -5776,7 +5824,7 @@
       <c r="P57" s="21">
         <v>0.21629999999999999</v>
       </c>
-      <c r="Q57" s="55">
+      <c r="Q57" s="54">
         <f t="shared" si="5"/>
         <v>3.2444999999999999</v>
       </c>
@@ -5806,7 +5854,7 @@
       <c r="H58" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="I58" s="60" t="s">
+      <c r="I58" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J58" s="14" t="s">
@@ -5831,7 +5879,7 @@
       <c r="P58" s="15">
         <v>1.1589</v>
       </c>
-      <c r="Q58" s="55">
+      <c r="Q58" s="54">
         <f t="shared" si="5"/>
         <v>18.542400000000001</v>
       </c>
@@ -5861,7 +5909,7 @@
       <c r="H59" s="20" t="s">
         <v>451</v>
       </c>
-      <c r="I59" s="60" t="s">
+      <c r="I59" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J59" s="20" t="s">
@@ -5886,7 +5934,7 @@
       <c r="P59" s="21">
         <v>9.7100000000000006E-2</v>
       </c>
-      <c r="Q59" s="55">
+      <c r="Q59" s="54">
         <f t="shared" si="5"/>
         <v>0.58260000000000001</v>
       </c>
@@ -5916,7 +5964,7 @@
       <c r="H60" s="14" t="s">
         <v>446</v>
       </c>
-      <c r="I60" s="60" t="s">
+      <c r="I60" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J60" s="14" t="s">
@@ -5941,7 +5989,7 @@
       <c r="P60" s="15">
         <v>4.1500000000000002E-2</v>
       </c>
-      <c r="Q60" s="55">
+      <c r="Q60" s="54">
         <f t="shared" si="5"/>
         <v>0.41500000000000004</v>
       </c>
@@ -5971,7 +6019,7 @@
       <c r="H61" s="20" t="s">
         <v>452</v>
       </c>
-      <c r="I61" s="60" t="s">
+      <c r="I61" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J61" s="20" t="s">
@@ -5996,7 +6044,7 @@
       <c r="P61" s="21">
         <v>0.2485</v>
       </c>
-      <c r="Q61" s="55">
+      <c r="Q61" s="54">
         <f t="shared" si="5"/>
         <v>7.4550000000000001</v>
       </c>
@@ -6026,7 +6074,7 @@
       <c r="H62" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="I62" s="60" t="s">
+      <c r="I62" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J62" s="14" t="s">
@@ -6051,7 +6099,7 @@
       <c r="P62" s="15">
         <v>9.7799999999999998E-2</v>
       </c>
-      <c r="Q62" s="55">
+      <c r="Q62" s="54">
         <f t="shared" si="5"/>
         <v>0.97799999999999998</v>
       </c>
@@ -6081,7 +6129,7 @@
       <c r="H63" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="I63" s="60" t="s">
+      <c r="I63" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J63" s="20" t="s">
@@ -6106,7 +6154,7 @@
       <c r="P63" s="21">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="Q63" s="55">
+      <c r="Q63" s="54">
         <f t="shared" si="5"/>
         <v>0.33999999999999997</v>
       </c>
@@ -6136,7 +6184,7 @@
       <c r="H64" s="14" t="s">
         <v>454</v>
       </c>
-      <c r="I64" s="60" t="s">
+      <c r="I64" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J64" s="14" t="s">
@@ -6161,7 +6209,7 @@
       <c r="P64" s="15">
         <v>0.35410000000000003</v>
       </c>
-      <c r="Q64" s="55">
+      <c r="Q64" s="54">
         <f t="shared" si="5"/>
         <v>3.5410000000000004</v>
       </c>
@@ -6191,7 +6239,7 @@
       <c r="H65" s="20" t="s">
         <v>455</v>
       </c>
-      <c r="I65" s="60" t="s">
+      <c r="I65" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J65" s="20" t="s">
@@ -6216,7 +6264,7 @@
       <c r="P65" s="15">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="Q65" s="55">
+      <c r="Q65" s="54">
         <f t="shared" si="5"/>
         <v>0.90800000000000003</v>
       </c>
@@ -6246,7 +6294,7 @@
       <c r="H66" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="I66" s="60" t="s">
+      <c r="I66" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J66" s="14" t="s">
@@ -6271,7 +6319,7 @@
       <c r="P66" s="21">
         <v>2.3400000000000001E-2</v>
       </c>
-      <c r="Q66" s="55">
+      <c r="Q66" s="54">
         <f t="shared" si="5"/>
         <v>0.46800000000000003</v>
       </c>
@@ -6301,7 +6349,7 @@
       <c r="H67" s="20" t="s">
         <v>456</v>
       </c>
-      <c r="I67" s="60" t="s">
+      <c r="I67" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J67" s="20" t="s">
@@ -6326,7 +6374,7 @@
       <c r="P67" s="15">
         <v>1.6E-2</v>
       </c>
-      <c r="Q67" s="55">
+      <c r="Q67" s="54">
         <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
@@ -6356,7 +6404,7 @@
       <c r="H68" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="I68" s="60" t="s">
+      <c r="I68" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J68" s="14" t="s">
@@ -6381,7 +6429,7 @@
       <c r="P68" s="21">
         <v>4.6199999999999998E-2</v>
       </c>
-      <c r="Q68" s="55">
+      <c r="Q68" s="54">
         <f t="shared" si="5"/>
         <v>0.46199999999999997</v>
       </c>
@@ -6411,7 +6459,7 @@
       <c r="H69" s="20" t="s">
         <v>458</v>
       </c>
-      <c r="I69" s="60" t="s">
+      <c r="I69" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J69" s="20" t="s">
@@ -6436,7 +6484,7 @@
       <c r="P69" s="21">
         <v>1.6E-2</v>
       </c>
-      <c r="Q69" s="55">
+      <c r="Q69" s="54">
         <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
@@ -6466,7 +6514,7 @@
       <c r="H70" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I70" s="60" t="s">
+      <c r="I70" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J70" s="14" t="s">
@@ -6491,7 +6539,7 @@
       <c r="P70" s="15">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q70" s="55">
+      <c r="Q70" s="54">
         <f t="shared" si="5"/>
         <v>6.9999999999999993E-2</v>
       </c>
@@ -6521,7 +6569,7 @@
       <c r="H71" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I71" s="60" t="s">
+      <c r="I71" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J71" s="20" t="s">
@@ -6546,7 +6594,7 @@
       <c r="P71" s="21">
         <v>2.8E-3</v>
       </c>
-      <c r="Q71" s="55">
+      <c r="Q71" s="54">
         <f t="shared" si="5"/>
         <v>0.27999999999999997</v>
       </c>
@@ -6576,7 +6624,7 @@
       <c r="H72" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I72" s="60" t="s">
+      <c r="I72" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J72" s="14" t="s">
@@ -6601,7 +6649,7 @@
       <c r="P72" s="15">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="Q72" s="55">
+      <c r="Q72" s="54">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
@@ -6631,7 +6679,7 @@
       <c r="H73" s="42" t="s">
         <v>425</v>
       </c>
-      <c r="I73" s="61" t="s">
+      <c r="I73" s="56" t="s">
         <v>653</v>
       </c>
       <c r="J73" s="42" t="s">
@@ -6656,7 +6704,7 @@
       <c r="P73" s="48" t="s">
         <v>639</v>
       </c>
-      <c r="Q73" s="55" t="s">
+      <c r="Q73" s="54" t="s">
         <v>639</v>
       </c>
       <c r="R73" s="49" t="s">
@@ -6687,7 +6735,7 @@
       <c r="H74" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I74" s="60" t="s">
+      <c r="I74" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J74" s="14" t="s">
@@ -6712,7 +6760,7 @@
       <c r="P74" s="15">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q74" s="55">
+      <c r="Q74" s="54">
         <f t="shared" si="5"/>
         <v>0.13999999999999999</v>
       </c>
@@ -6742,7 +6790,7 @@
       <c r="H75" s="42" t="s">
         <v>425</v>
       </c>
-      <c r="I75" s="61" t="s">
+      <c r="I75" s="56" t="s">
         <v>653</v>
       </c>
       <c r="J75" s="42" t="s">
@@ -6767,7 +6815,7 @@
       <c r="P75" s="48" t="s">
         <v>639</v>
       </c>
-      <c r="Q75" s="55" t="s">
+      <c r="Q75" s="54" t="s">
         <v>639</v>
       </c>
       <c r="R75" s="49" t="s">
@@ -6798,7 +6846,7 @@
       <c r="H76" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I76" s="60" t="s">
+      <c r="I76" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J76" s="14" t="s">
@@ -6823,7 +6871,7 @@
       <c r="P76" s="15">
         <v>1E-3</v>
       </c>
-      <c r="Q76" s="55">
+      <c r="Q76" s="54">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
@@ -6853,7 +6901,7 @@
       <c r="H77" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I77" s="60" t="s">
+      <c r="I77" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J77" s="20" t="s">
@@ -6878,8 +6926,8 @@
       <c r="P77" s="21">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q77" s="55">
-        <f t="shared" ref="Q77:Q124" si="38">P77*N77</f>
+      <c r="Q77" s="54">
+        <f t="shared" ref="Q77:Q122" si="38">P77*N77</f>
         <v>6.9999999999999993E-2</v>
       </c>
       <c r="R77" s="20"/>
@@ -6908,7 +6956,7 @@
       <c r="H78" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I78" s="60" t="s">
+      <c r="I78" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J78" s="14" t="s">
@@ -6933,7 +6981,7 @@
       <c r="P78" s="15">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q78" s="55">
+      <c r="Q78" s="54">
         <f t="shared" si="38"/>
         <v>0.12</v>
       </c>
@@ -6963,7 +7011,7 @@
       <c r="H79" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I79" s="60" t="s">
+      <c r="I79" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J79" s="20" t="s">
@@ -6988,7 +7036,7 @@
       <c r="P79" s="21">
         <v>2.7400000000000001E-2</v>
       </c>
-      <c r="Q79" s="55">
+      <c r="Q79" s="54">
         <f t="shared" si="38"/>
         <v>0.54800000000000004</v>
       </c>
@@ -7018,7 +7066,7 @@
       <c r="H80" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I80" s="60" t="s">
+      <c r="I80" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J80" s="14" t="s">
@@ -7043,7 +7091,7 @@
       <c r="P80" s="15">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="Q80" s="55">
+      <c r="Q80" s="54">
         <f t="shared" si="38"/>
         <v>1.01</v>
       </c>
@@ -7073,7 +7121,7 @@
       <c r="H81" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I81" s="60" t="s">
+      <c r="I81" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J81" s="20" t="s">
@@ -7098,7 +7146,7 @@
       <c r="P81" s="21">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q81" s="55">
+      <c r="Q81" s="54">
         <f t="shared" si="38"/>
         <v>0.06</v>
       </c>
@@ -7128,7 +7176,7 @@
       <c r="H82" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I82" s="60" t="s">
+      <c r="I82" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J82" s="14" t="s">
@@ -7153,7 +7201,7 @@
       <c r="P82" s="15">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q82" s="55">
+      <c r="Q82" s="54">
         <f t="shared" si="38"/>
         <v>6.9999999999999993E-2</v>
       </c>
@@ -7183,7 +7231,7 @@
       <c r="H83" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I83" s="60" t="s">
+      <c r="I83" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J83" s="20" t="s">
@@ -7208,7 +7256,7 @@
       <c r="P83" s="15">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q83" s="55">
+      <c r="Q83" s="54">
         <f t="shared" si="38"/>
         <v>0.06</v>
       </c>
@@ -7238,7 +7286,7 @@
       <c r="H84" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="I84" s="60" t="s">
+      <c r="I84" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J84" s="14" t="s">
@@ -7263,7 +7311,7 @@
       <c r="P84" s="21">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q84" s="55">
+      <c r="Q84" s="54">
         <f t="shared" si="38"/>
         <v>6.9999999999999993E-2</v>
       </c>
@@ -7291,7 +7339,7 @@
         <v>391</v>
       </c>
       <c r="H85" s="20"/>
-      <c r="I85" s="60" t="s">
+      <c r="I85" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J85" s="20" t="s">
@@ -7316,7 +7364,7 @@
       <c r="P85" s="15">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q85" s="55">
+      <c r="Q85" s="54">
         <f t="shared" si="38"/>
         <v>0.06</v>
       </c>
@@ -7346,7 +7394,7 @@
       <c r="H86" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I86" s="60" t="s">
+      <c r="I86" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J86" s="14" t="s">
@@ -7371,7 +7419,7 @@
       <c r="P86" s="21">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q86" s="55">
+      <c r="Q86" s="54">
         <f t="shared" si="38"/>
         <v>0.06</v>
       </c>
@@ -7401,7 +7449,7 @@
       <c r="H87" s="20" t="s">
         <v>460</v>
       </c>
-      <c r="I87" s="60" t="s">
+      <c r="I87" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J87" s="20" t="s">
@@ -7426,7 +7474,7 @@
       <c r="P87" s="15">
         <v>2.07E-2</v>
       </c>
-      <c r="Q87" s="55">
+      <c r="Q87" s="54">
         <f t="shared" si="38"/>
         <v>0.41399999999999998</v>
       </c>
@@ -7456,7 +7504,7 @@
       <c r="H88" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I88" s="60" t="s">
+      <c r="I88" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J88" s="14" t="s">
@@ -7481,7 +7529,7 @@
       <c r="P88" s="15">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q88" s="55">
+      <c r="Q88" s="54">
         <f t="shared" si="38"/>
         <v>0.12</v>
       </c>
@@ -7511,7 +7559,7 @@
       <c r="H89" s="20" t="s">
         <v>460</v>
       </c>
-      <c r="I89" s="60" t="s">
+      <c r="I89" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J89" s="20" t="s">
@@ -7536,7 +7584,7 @@
       <c r="P89" s="21">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="Q89" s="55">
+      <c r="Q89" s="54">
         <f t="shared" si="38"/>
         <v>0.84</v>
       </c>
@@ -7566,7 +7614,7 @@
       <c r="H90" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="I90" s="60" t="s">
+      <c r="I90" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J90" s="14" t="s">
@@ -7591,7 +7639,7 @@
       <c r="P90" s="15">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="Q90" s="55">
+      <c r="Q90" s="54">
         <f t="shared" si="38"/>
         <v>0.31</v>
       </c>
@@ -7621,7 +7669,7 @@
       <c r="H91" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I91" s="60" t="s">
+      <c r="I91" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J91" s="20" t="s">
@@ -7646,7 +7694,7 @@
       <c r="P91" s="21">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q91" s="55">
+      <c r="Q91" s="54">
         <f t="shared" si="38"/>
         <v>0.11</v>
       </c>
@@ -7676,7 +7724,7 @@
       <c r="H92" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I92" s="60" t="s">
+      <c r="I92" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J92" s="14" t="s">
@@ -7701,7 +7749,7 @@
       <c r="P92" s="15">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="Q92" s="55">
+      <c r="Q92" s="54">
         <f t="shared" si="38"/>
         <v>0.4</v>
       </c>
@@ -7731,7 +7779,7 @@
       <c r="H93" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I93" s="60" t="s">
+      <c r="I93" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J93" s="20" t="s">
@@ -7756,7 +7804,7 @@
       <c r="P93" s="21">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="Q93" s="55">
+      <c r="Q93" s="54">
         <f t="shared" si="38"/>
         <v>0.09</v>
       </c>
@@ -7786,7 +7834,7 @@
       <c r="H94" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I94" s="60" t="s">
+      <c r="I94" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J94" s="14" t="s">
@@ -7811,7 +7859,7 @@
       <c r="P94" s="15">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q94" s="55">
+      <c r="Q94" s="54">
         <f t="shared" si="38"/>
         <v>0.11</v>
       </c>
@@ -7841,7 +7889,7 @@
       <c r="H95" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I95" s="60" t="s">
+      <c r="I95" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J95" s="20" t="s">
@@ -7866,7 +7914,7 @@
       <c r="P95" s="21">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q95" s="55">
+      <c r="Q95" s="54">
         <f t="shared" si="38"/>
         <v>0.11</v>
       </c>
@@ -7896,7 +7944,7 @@
       <c r="H96" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I96" s="60" t="s">
+      <c r="I96" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J96" s="14" t="s">
@@ -7921,7 +7969,7 @@
       <c r="P96" s="21">
         <v>1E-3</v>
       </c>
-      <c r="Q96" s="55">
+      <c r="Q96" s="54">
         <f t="shared" si="38"/>
         <v>0.1</v>
       </c>
@@ -7951,7 +7999,7 @@
       <c r="H97" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I97" s="60" t="s">
+      <c r="I97" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J97" s="20" t="s">
@@ -7976,7 +8024,7 @@
       <c r="P97" s="21">
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="Q97" s="55">
+      <c r="Q97" s="54">
         <f t="shared" si="38"/>
         <v>1.02</v>
       </c>
@@ -8006,7 +8054,7 @@
       <c r="H98" s="42" t="s">
         <v>425</v>
       </c>
-      <c r="I98" s="61" t="s">
+      <c r="I98" s="56" t="s">
         <v>653</v>
       </c>
       <c r="J98" s="42" t="s">
@@ -8031,7 +8079,7 @@
       <c r="P98" s="48" t="s">
         <v>639</v>
       </c>
-      <c r="Q98" s="55" t="s">
+      <c r="Q98" s="54" t="s">
         <v>639</v>
       </c>
       <c r="R98" s="49" t="s">
@@ -8062,7 +8110,7 @@
       <c r="H99" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I99" s="60" t="s">
+      <c r="I99" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J99" s="20" t="s">
@@ -8087,7 +8135,7 @@
       <c r="P99" s="21">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="Q99" s="55">
+      <c r="Q99" s="54">
         <f t="shared" si="38"/>
         <v>0.09</v>
       </c>
@@ -8117,7 +8165,7 @@
       <c r="H100" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I100" s="60" t="s">
+      <c r="I100" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J100" s="14" t="s">
@@ -8142,7 +8190,7 @@
       <c r="P100" s="15">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q100" s="55">
+      <c r="Q100" s="54">
         <f t="shared" si="38"/>
         <v>0.12</v>
       </c>
@@ -8172,7 +8220,7 @@
       <c r="H101" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="I101" s="60" t="s">
+      <c r="I101" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J101" s="20" t="s">
@@ -8197,7 +8245,7 @@
       <c r="P101" s="21">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="Q101" s="55">
+      <c r="Q101" s="54">
         <f t="shared" si="38"/>
         <v>0.41000000000000003</v>
       </c>
@@ -8227,7 +8275,7 @@
       <c r="H102" s="14" t="s">
         <v>462</v>
       </c>
-      <c r="I102" s="60" t="s">
+      <c r="I102" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J102" s="14" t="s">
@@ -8252,7 +8300,7 @@
       <c r="P102" s="15">
         <v>0.1552</v>
       </c>
-      <c r="Q102" s="55">
+      <c r="Q102" s="54">
         <f t="shared" si="38"/>
         <v>3.1040000000000001</v>
       </c>
@@ -8282,7 +8330,7 @@
       <c r="H103" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="I103" s="60" t="s">
+      <c r="I103" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J103" s="20" t="s">
@@ -8307,7 +8355,7 @@
       <c r="P103" s="21">
         <v>0.5262</v>
       </c>
-      <c r="Q103" s="55">
+      <c r="Q103" s="54">
         <f t="shared" si="38"/>
         <v>11.0502</v>
       </c>
@@ -8337,7 +8385,7 @@
       <c r="H104" s="14" t="s">
         <v>464</v>
       </c>
-      <c r="I104" s="60" t="s">
+      <c r="I104" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J104" s="14" t="s">
@@ -8362,7 +8410,7 @@
       <c r="P104" s="15">
         <v>0.36420000000000002</v>
       </c>
-      <c r="Q104" s="55">
+      <c r="Q104" s="54">
         <f t="shared" si="38"/>
         <v>2.1852</v>
       </c>
@@ -8392,7 +8440,7 @@
       <c r="H105" s="20" t="s">
         <v>465</v>
       </c>
-      <c r="I105" s="60" t="s">
+      <c r="I105" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J105" s="20" t="s">
@@ -8417,7 +8465,7 @@
       <c r="P105" s="15">
         <v>6.5850999999999997</v>
       </c>
-      <c r="Q105" s="55">
+      <c r="Q105" s="54">
         <f t="shared" si="38"/>
         <v>39.510599999999997</v>
       </c>
@@ -8447,7 +8495,7 @@
       <c r="H106" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="I106" s="60" t="s">
+      <c r="I106" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J106" s="14" t="s">
@@ -8472,7 +8520,7 @@
       <c r="P106" s="21">
         <v>2.6966000000000001</v>
       </c>
-      <c r="Q106" s="55">
+      <c r="Q106" s="54">
         <f t="shared" si="38"/>
         <v>16.179600000000001</v>
       </c>
@@ -8502,7 +8550,7 @@
       <c r="H107" s="20" t="s">
         <v>467</v>
       </c>
-      <c r="I107" s="60" t="s">
+      <c r="I107" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J107" s="20" t="s">
@@ -8527,7 +8575,7 @@
       <c r="P107" s="21">
         <v>0.96589999999999998</v>
       </c>
-      <c r="Q107" s="55">
+      <c r="Q107" s="54">
         <f t="shared" si="38"/>
         <v>5.7953999999999999</v>
       </c>
@@ -8557,7 +8605,7 @@
       <c r="H108" s="14" t="s">
         <v>467</v>
       </c>
-      <c r="I108" s="60" t="s">
+      <c r="I108" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J108" s="14" t="s">
@@ -8582,7 +8630,7 @@
       <c r="P108" s="15">
         <v>1.0339</v>
       </c>
-      <c r="Q108" s="55">
+      <c r="Q108" s="54">
         <f t="shared" si="38"/>
         <v>6.2034000000000002</v>
       </c>
@@ -8612,7 +8660,7 @@
       <c r="H109" s="20" t="s">
         <v>468</v>
       </c>
-      <c r="I109" s="60" t="s">
+      <c r="I109" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J109" s="20" t="s">
@@ -8637,7 +8685,7 @@
       <c r="P109" s="21">
         <v>0.77139999999999997</v>
       </c>
-      <c r="Q109" s="55">
+      <c r="Q109" s="54">
         <f t="shared" si="38"/>
         <v>4.6284000000000001</v>
       </c>
@@ -8667,7 +8715,7 @@
       <c r="H110" s="14" t="s">
         <v>435</v>
       </c>
-      <c r="I110" s="60" t="s">
+      <c r="I110" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J110" s="14" t="s">
@@ -8692,7 +8740,7 @@
       <c r="P110" s="15">
         <v>0.40949999999999998</v>
       </c>
-      <c r="Q110" s="55">
+      <c r="Q110" s="54">
         <f t="shared" si="38"/>
         <v>2.4569999999999999</v>
       </c>
@@ -8722,7 +8770,7 @@
       <c r="H111" s="20" t="s">
         <v>469</v>
       </c>
-      <c r="I111" s="60" t="s">
+      <c r="I111" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J111" s="20" t="s">
@@ -8747,7 +8795,7 @@
       <c r="P111" s="21">
         <v>0.1729</v>
       </c>
-      <c r="Q111" s="55">
+      <c r="Q111" s="54">
         <f t="shared" si="38"/>
         <v>1.7290000000000001</v>
       </c>
@@ -8777,7 +8825,7 @@
       <c r="H112" s="14" t="s">
         <v>467</v>
       </c>
-      <c r="I112" s="60" t="s">
+      <c r="I112" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J112" s="14" t="s">
@@ -8802,7 +8850,7 @@
       <c r="P112" s="15">
         <v>2.9133</v>
       </c>
-      <c r="Q112" s="55">
+      <c r="Q112" s="54">
         <f t="shared" si="38"/>
         <v>17.479800000000001</v>
       </c>
@@ -8832,7 +8880,7 @@
       <c r="H113" s="20" t="s">
         <v>470</v>
       </c>
-      <c r="I113" s="60" t="s">
+      <c r="I113" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J113" s="20" t="s">
@@ -8857,7 +8905,7 @@
       <c r="P113" s="21">
         <v>2.6192000000000002</v>
       </c>
-      <c r="Q113" s="55">
+      <c r="Q113" s="54">
         <f t="shared" si="38"/>
         <v>15.715200000000001</v>
       </c>
@@ -8887,7 +8935,7 @@
       <c r="H114" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="I114" s="60" t="s">
+      <c r="I114" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J114" s="14" t="s">
@@ -8912,7 +8960,7 @@
       <c r="P114" s="15">
         <v>0.28999999999999998</v>
       </c>
-      <c r="Q114" s="55">
+      <c r="Q114" s="54">
         <f t="shared" si="38"/>
         <v>2.9</v>
       </c>
@@ -8942,7 +8990,7 @@
       <c r="H115" s="20" t="s">
         <v>467</v>
       </c>
-      <c r="I115" s="60" t="s">
+      <c r="I115" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J115" s="20" t="s">
@@ -8967,7 +9015,7 @@
       <c r="P115" s="21">
         <v>0.3483</v>
       </c>
-      <c r="Q115" s="55">
+      <c r="Q115" s="54">
         <f t="shared" si="38"/>
         <v>2.0897999999999999</v>
       </c>
@@ -8997,7 +9045,7 @@
       <c r="H116" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="I116" s="60" t="s">
+      <c r="I116" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J116" s="14" t="s">
@@ -9022,7 +9070,7 @@
       <c r="P116" s="21">
         <v>0.33610000000000001</v>
       </c>
-      <c r="Q116" s="55">
+      <c r="Q116" s="54">
         <f t="shared" si="38"/>
         <v>2.0165999999999999</v>
       </c>
@@ -9052,7 +9100,7 @@
       <c r="H117" s="20" t="s">
         <v>467</v>
       </c>
-      <c r="I117" s="60" t="s">
+      <c r="I117" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J117" s="20" t="s">
@@ -9077,7 +9125,7 @@
       <c r="P117" s="15">
         <v>2.984</v>
       </c>
-      <c r="Q117" s="55">
+      <c r="Q117" s="54">
         <f t="shared" si="38"/>
         <v>47.744</v>
       </c>
@@ -9107,7 +9155,7 @@
       <c r="H118" s="14" t="s">
         <v>472</v>
       </c>
-      <c r="I118" s="60" t="s">
+      <c r="I118" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J118" s="14" t="s">
@@ -9132,7 +9180,7 @@
       <c r="P118" s="15">
         <v>8.6266999999999996</v>
       </c>
-      <c r="Q118" s="55">
+      <c r="Q118" s="54">
         <f t="shared" si="38"/>
         <v>51.760199999999998</v>
       </c>
@@ -9162,7 +9210,7 @@
       <c r="H119" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="I119" s="60" t="s">
+      <c r="I119" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J119" s="20" t="s">
@@ -9187,7 +9235,7 @@
       <c r="P119" s="21">
         <v>0.45850000000000002</v>
       </c>
-      <c r="Q119" s="55">
+      <c r="Q119" s="54">
         <f t="shared" si="38"/>
         <v>2.7510000000000003</v>
       </c>
@@ -9217,7 +9265,7 @@
       <c r="H120" s="43" t="s">
         <v>473</v>
       </c>
-      <c r="I120" s="61" t="s">
+      <c r="I120" s="56" t="s">
         <v>653</v>
       </c>
       <c r="J120" s="43" t="s">
@@ -9242,7 +9290,7 @@
       <c r="P120" s="48" t="s">
         <v>639</v>
       </c>
-      <c r="Q120" s="55" t="s">
+      <c r="Q120" s="54" t="s">
         <v>639</v>
       </c>
       <c r="R120" s="49" t="s">
@@ -9273,7 +9321,7 @@
       <c r="H121" s="20" t="s">
         <v>474</v>
       </c>
-      <c r="I121" s="60" t="s">
+      <c r="I121" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J121" s="20" t="s">
@@ -9298,7 +9346,7 @@
       <c r="P121" s="21">
         <v>0.30080000000000001</v>
       </c>
-      <c r="Q121" s="55">
+      <c r="Q121" s="54">
         <f t="shared" si="38"/>
         <v>3.008</v>
       </c>
@@ -9328,7 +9376,7 @@
       <c r="H122" s="14" t="s">
         <v>475</v>
       </c>
-      <c r="I122" s="60" t="s">
+      <c r="I122" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J122" s="14" t="s">
@@ -9353,7 +9401,7 @@
       <c r="P122" s="15">
         <v>6.5600000000000006E-2</v>
       </c>
-      <c r="Q122" s="55">
+      <c r="Q122" s="54">
         <f t="shared" si="38"/>
         <v>0.65600000000000003</v>
       </c>
@@ -9383,7 +9431,7 @@
       <c r="H123" s="20" t="s">
         <v>473</v>
       </c>
-      <c r="I123" s="60" t="s">
+      <c r="I123" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J123" s="20" t="s">
@@ -9396,7 +9444,7 @@
         <v>1</v>
       </c>
       <c r="M123" s="20">
-        <f t="shared" ref="M123:M124" si="61">L123*5</f>
+        <f t="shared" ref="M123:M128" si="61">L123*5</f>
         <v>5</v>
       </c>
       <c r="N123" s="20">
@@ -9408,16 +9456,16 @@
       <c r="P123" s="21">
         <v>0.25950000000000001</v>
       </c>
-      <c r="Q123" s="55">
+      <c r="Q123" s="54">
         <f>P123*N123</f>
         <v>2.5950000000000002</v>
       </c>
       <c r="R123" s="20"/>
     </row>
-    <row r="124" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
-      <c r="B124" s="17">
-        <f t="shared" si="0"/>
+      <c r="B124" s="16">
+        <f t="shared" ref="B124:B127" si="62">ROW(B124) - ROW($B$7)</f>
         <v>117</v>
       </c>
       <c r="C124" s="23" t="s">
@@ -9438,8 +9486,8 @@
       <c r="H124" s="20" t="s">
         <v>639</v>
       </c>
-      <c r="I124" s="60" t="s">
-        <v>639</v>
+      <c r="I124" s="55" t="s">
+        <v>653</v>
       </c>
       <c r="J124" s="20" t="s">
         <v>639</v>
@@ -9451,7 +9499,7 @@
         <v>1</v>
       </c>
       <c r="M124" s="20">
-        <f t="shared" si="61"/>
+        <f>L124*5</f>
         <v>5</v>
       </c>
       <c r="N124" s="20">
@@ -9463,70 +9511,290 @@
       <c r="P124" s="21">
         <v>7.99</v>
       </c>
-      <c r="Q124" s="55">
+      <c r="Q124" s="54">
         <f>P124*N124</f>
         <v>39.950000000000003</v>
       </c>
       <c r="R124" s="20"/>
     </row>
-    <row r="125" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
-      <c r="K125" s="1"/>
-      <c r="L125" s="1"/>
-      <c r="M125" s="1"/>
-      <c r="N125" s="57" t="s">
+      <c r="B125" s="16">
+        <f t="shared" si="62"/>
+        <v>118</v>
+      </c>
+      <c r="C125" s="22" t="s">
+        <v>654</v>
+      </c>
+      <c r="D125" s="14" t="s">
+        <v>658</v>
+      </c>
+      <c r="E125" s="44" t="s">
+        <v>659</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="G125" s="44" t="s">
+        <v>660</v>
+      </c>
+      <c r="H125" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="I125" s="55" t="s">
+        <v>653</v>
+      </c>
+      <c r="J125" s="20" t="s">
+        <v>673</v>
+      </c>
+      <c r="K125" s="45" t="s">
+        <v>639</v>
+      </c>
+      <c r="L125" s="20">
+        <v>8</v>
+      </c>
+      <c r="M125" s="20">
+        <f>L125*5</f>
+        <v>40</v>
+      </c>
+      <c r="N125" s="20">
+        <v>40</v>
+      </c>
+      <c r="O125" s="50" t="s">
+        <v>640</v>
+      </c>
+      <c r="P125" s="15">
+        <v>2.01E-2</v>
+      </c>
+      <c r="Q125" s="54">
+        <f>P125*N125</f>
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="R125" s="20"/>
+    </row>
+    <row r="126" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A126" s="1"/>
+      <c r="B126" s="16">
+        <f t="shared" si="62"/>
+        <v>119</v>
+      </c>
+      <c r="C126" s="22" t="s">
+        <v>654</v>
+      </c>
+      <c r="D126" s="14" t="s">
+        <v>661</v>
+      </c>
+      <c r="E126" s="44" t="s">
+        <v>662</v>
+      </c>
+      <c r="F126" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="G126" s="44">
+        <v>50173</v>
+      </c>
+      <c r="H126" s="14" t="s">
+        <v>663</v>
+      </c>
+      <c r="I126" s="55" t="s">
+        <v>653</v>
+      </c>
+      <c r="J126" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="K126" s="45" t="s">
+        <v>639</v>
+      </c>
+      <c r="L126" s="20">
+        <v>2</v>
+      </c>
+      <c r="M126" s="20">
+        <f>L126*5</f>
+        <v>10</v>
+      </c>
+      <c r="N126" s="20">
+        <v>10</v>
+      </c>
+      <c r="O126" s="50" t="s">
+        <v>640</v>
+      </c>
+      <c r="P126" s="15">
+        <v>1.3977999999999999</v>
+      </c>
+      <c r="Q126" s="54">
+        <f>P126*N126</f>
+        <v>13.978</v>
+      </c>
+      <c r="R126" s="20"/>
+    </row>
+    <row r="127" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A127" s="1"/>
+      <c r="B127" s="16">
+        <f t="shared" si="62"/>
+        <v>120</v>
+      </c>
+      <c r="C127" s="23" t="s">
+        <v>654</v>
+      </c>
+      <c r="D127" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="20" t="s">
+        <v>664</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="G127" s="20" t="s">
+        <v>665</v>
+      </c>
+      <c r="H127" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="I127" s="55" t="s">
+        <v>653</v>
+      </c>
+      <c r="J127" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="K127" s="45" t="s">
+        <v>639</v>
+      </c>
+      <c r="L127" s="20">
+        <v>1</v>
+      </c>
+      <c r="M127" s="20">
+        <f>L127*5</f>
+        <v>5</v>
+      </c>
+      <c r="N127" s="20">
+        <v>5</v>
+      </c>
+      <c r="O127" s="47" t="s">
+        <v>640</v>
+      </c>
+      <c r="P127" s="21">
+        <v>8.7099999999999997E-2</v>
+      </c>
+      <c r="Q127" s="54">
+        <f t="shared" ref="Q127:Q128" si="63">P127*N127</f>
+        <v>0.4355</v>
+      </c>
+      <c r="R127" s="20"/>
+    </row>
+    <row r="128" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="1"/>
+      <c r="B128" s="17">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+      <c r="C128" s="23" t="s">
+        <v>654</v>
+      </c>
+      <c r="D128" s="20" t="s">
+        <v>667</v>
+      </c>
+      <c r="E128" s="20" t="s">
+        <v>668</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="G128" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="H128" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="I128" s="55" t="s">
+        <v>653</v>
+      </c>
+      <c r="J128" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="K128" s="45" t="s">
+        <v>639</v>
+      </c>
+      <c r="L128" s="20">
+        <v>1</v>
+      </c>
+      <c r="M128" s="20">
+        <f>L128*5</f>
+        <v>5</v>
+      </c>
+      <c r="N128" s="20">
+        <v>5</v>
+      </c>
+      <c r="O128" s="47" t="s">
+        <v>640</v>
+      </c>
+      <c r="P128" s="21">
+        <v>1.8872</v>
+      </c>
+      <c r="Q128" s="54">
+        <f t="shared" si="63"/>
+        <v>9.4359999999999999</v>
+      </c>
+      <c r="R128" s="20"/>
+    </row>
+    <row r="129" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="1"/>
+      <c r="N129" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="O125" s="58"/>
-      <c r="P125" s="59"/>
-      <c r="Q125" s="18">
-        <f>SUM(Q8:Q124)</f>
-        <v>389.02409999999998</v>
-      </c>
-      <c r="R125" s="1"/>
-    </row>
-    <row r="126" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="1"/>
-      <c r="M126" s="1"/>
-      <c r="N126" s="57" t="s">
+      <c r="O129" s="59"/>
+      <c r="P129" s="60"/>
+      <c r="Q129" s="18">
+        <f>SUM(Q8:Q128)</f>
+        <v>413.67759999999993</v>
+      </c>
+      <c r="R129" s="1"/>
+    </row>
+    <row r="130" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
+      <c r="K130" s="1"/>
+      <c r="L130" s="1"/>
+      <c r="M130" s="1"/>
+      <c r="N130" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="O126" s="58"/>
-      <c r="P126" s="58"/>
-      <c r="Q126" s="19">
-        <f>Q125/5</f>
-        <v>77.804819999999992</v>
-      </c>
-      <c r="R126" s="1"/>
-    </row>
-    <row r="138" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M138" s="38"/>
+      <c r="O130" s="59"/>
+      <c r="P130" s="59"/>
+      <c r="Q130" s="19">
+        <f>Q129/5</f>
+        <v>82.73551999999998</v>
+      </c>
+      <c r="R130" s="1"/>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M142" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N125:P125"/>
-    <mergeCell ref="N126:P126"/>
+    <mergeCell ref="N129:P129"/>
+    <mergeCell ref="N130:P130"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O121" r:id="rId1"/>
@@ -9641,8 +9909,12 @@
     <hyperlink ref="O111" r:id="rId110"/>
     <hyperlink ref="O119" r:id="rId111"/>
     <hyperlink ref="O124" r:id="rId112"/>
+    <hyperlink ref="O125" r:id="rId113"/>
+    <hyperlink ref="O126" r:id="rId114"/>
+    <hyperlink ref="O127" r:id="rId115"/>
+    <hyperlink ref="O128" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId113"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId117"/>
 </worksheet>
 </file>
--- a/Design Files/Control-Board-v1.0/BOM/eSpark-BOM-Control-Board-v1.0.xlsx
+++ b/Design Files/Control-Board-v1.0/BOM/eSpark-BOM-Control-Board-v1.0.xlsx
@@ -1989,9 +1989,6 @@
     <t>3.5" inch 320*480 32P/0.5 ST7796 8/16 MCU Parallel 3/4 SPI TFT Color LCD Module Display Screen Resistive Capacitive Touch Panel</t>
   </si>
   <si>
-    <t>CN-TN-ST7796-NTP</t>
-  </si>
-  <si>
     <t>Aliexpress</t>
   </si>
   <si>
@@ -2044,6 +2041,9 @@
   </si>
   <si>
     <t>C3015021</t>
+  </si>
+  <si>
+    <t>CS-IPS-ST7796-NTP</t>
   </si>
 </sst>
 </file>
@@ -9444,7 +9444,7 @@
         <v>1</v>
       </c>
       <c r="M123" s="20">
-        <f t="shared" ref="M123:M128" si="61">L123*5</f>
+        <f t="shared" ref="M123" si="61">L123*5</f>
         <v>5</v>
       </c>
       <c r="N123" s="20">
@@ -9481,7 +9481,7 @@
         <v>638</v>
       </c>
       <c r="G124" s="20" t="s">
-        <v>656</v>
+        <v>674</v>
       </c>
       <c r="H124" s="20" t="s">
         <v>639</v>
@@ -9506,7 +9506,7 @@
         <v>5</v>
       </c>
       <c r="O124" s="47" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="P124" s="21">
         <v>7.99</v>
@@ -9527,16 +9527,16 @@
         <v>654</v>
       </c>
       <c r="D125" s="14" t="s">
+        <v>657</v>
+      </c>
+      <c r="E125" s="44" t="s">
         <v>658</v>
-      </c>
-      <c r="E125" s="44" t="s">
-        <v>659</v>
       </c>
       <c r="F125" s="14" t="s">
         <v>638</v>
       </c>
       <c r="G125" s="44" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H125" s="14" t="s">
         <v>449</v>
@@ -9545,7 +9545,7 @@
         <v>653</v>
       </c>
       <c r="J125" s="20" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="K125" s="45" t="s">
         <v>639</v>
@@ -9582,10 +9582,10 @@
         <v>654</v>
       </c>
       <c r="D126" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="E126" s="44" t="s">
         <v>661</v>
-      </c>
-      <c r="E126" s="44" t="s">
-        <v>662</v>
       </c>
       <c r="F126" s="14" t="s">
         <v>638</v>
@@ -9594,13 +9594,13 @@
         <v>50173</v>
       </c>
       <c r="H126" s="14" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I126" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J126" s="20" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="K126" s="45" t="s">
         <v>639</v>
@@ -9640,22 +9640,22 @@
         <v>11</v>
       </c>
       <c r="E127" s="20" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F127" s="14" t="s">
         <v>638</v>
       </c>
       <c r="G127" s="20" t="s">
+        <v>664</v>
+      </c>
+      <c r="H127" s="20" t="s">
         <v>665</v>
       </c>
-      <c r="H127" s="20" t="s">
-        <v>666</v>
-      </c>
       <c r="I127" s="55" t="s">
         <v>653</v>
       </c>
       <c r="J127" s="20" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="K127" s="45" t="s">
         <v>639</v>
@@ -9692,25 +9692,25 @@
         <v>654</v>
       </c>
       <c r="D128" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="E128" s="20" t="s">
         <v>667</v>
-      </c>
-      <c r="E128" s="20" t="s">
-        <v>668</v>
       </c>
       <c r="F128" s="14" t="s">
         <v>638</v>
       </c>
       <c r="G128" s="20" t="s">
+        <v>668</v>
+      </c>
+      <c r="H128" s="20" t="s">
         <v>669</v>
       </c>
-      <c r="H128" s="20" t="s">
+      <c r="I128" s="55" t="s">
+        <v>653</v>
+      </c>
+      <c r="J128" s="20" t="s">
         <v>670</v>
-      </c>
-      <c r="I128" s="55" t="s">
-        <v>653</v>
-      </c>
-      <c r="J128" s="20" t="s">
-        <v>671</v>
       </c>
       <c r="K128" s="45" t="s">
         <v>639</v>

--- a/Design Files/Control-Board-v1.0/BOM/eSpark-BOM-Control-Board-v1.0.xlsx
+++ b/Design Files/Control-Board-v1.0/BOM/eSpark-BOM-Control-Board-v1.0.xlsx
@@ -306,9 +306,6 @@
     <t>LED1, LED2, LED3, LED5</t>
   </si>
   <si>
-    <t>LED4, LED?</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -408,9 +405,6 @@
     <t>R169</t>
   </si>
   <si>
-    <t>R?</t>
-  </si>
-  <si>
     <t>RN1, RN2, RN3</t>
   </si>
   <si>
@@ -2044,6 +2038,12 @@
   </si>
   <si>
     <t>CS-IPS-ST7796-NTP</t>
+  </si>
+  <si>
+    <t>LED4, LED6</t>
+  </si>
+  <si>
+    <t>R89</t>
   </si>
 </sst>
 </file>
@@ -2899,6 +2899,9 @@
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2930,7 +2933,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="40" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -2954,7 +2957,7 @@
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="41" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="30"/>
@@ -3041,46 +3044,46 @@
         <v>36</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I7" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="M7" s="12" t="s">
         <v>630</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="K7" s="12" t="s">
+      <c r="N7" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>627</v>
-      </c>
-      <c r="M7" s="12" t="s">
+      <c r="O7" s="12" t="s">
         <v>632</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="P7" s="12" t="s">
         <v>633</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="Q7" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="R7" s="12" t="s">
         <v>635</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>636</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3096,25 +3099,25 @@
         <v>37</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I8" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="L8" s="14">
         <v>2</v>
@@ -3127,7 +3130,7 @@
         <v>20</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P8" s="15">
         <v>2.0799999999999999E-2</v>
@@ -3151,25 +3154,25 @@
         <v>38</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I9" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="K9" s="45" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="L9" s="20">
         <v>3</v>
@@ -3182,7 +3185,7 @@
         <v>20</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P9" s="21">
         <v>0.14480000000000001</v>
@@ -3206,25 +3209,25 @@
         <v>39</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I10" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="L10" s="14">
         <v>13</v>
@@ -3237,7 +3240,7 @@
         <v>100</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P10" s="15">
         <v>1.6000000000000001E-3</v>
@@ -3261,25 +3264,25 @@
         <v>40</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H11" s="42" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I11" s="56" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J11" s="42" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K11" s="46" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="L11" s="42">
         <v>2</v>
@@ -3289,19 +3292,19 @@
         <v>10</v>
       </c>
       <c r="N11" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="O11" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="P11" s="48" t="s">
+        <v>637</v>
+      </c>
+      <c r="Q11" s="48" t="s">
+        <v>637</v>
+      </c>
+      <c r="R11" s="49" t="s">
         <v>639</v>
-      </c>
-      <c r="O11" s="43" t="s">
-        <v>639</v>
-      </c>
-      <c r="P11" s="48" t="s">
-        <v>639</v>
-      </c>
-      <c r="Q11" s="48" t="s">
-        <v>639</v>
-      </c>
-      <c r="R11" s="49" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -3317,25 +3320,25 @@
         <v>41</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I12" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L12" s="14">
         <v>4</v>
@@ -3348,7 +3351,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="51" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P12" s="53">
         <v>2.0999999999999999E-3</v>
@@ -3372,25 +3375,25 @@
         <v>42</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I13" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K13" s="45" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="L13" s="20">
         <v>1</v>
@@ -3403,7 +3406,7 @@
         <v>50</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P13" s="21">
         <v>1.7500000000000002E-2</v>
@@ -3427,25 +3430,25 @@
         <v>43</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I14" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="L14" s="14">
         <v>20</v>
@@ -3458,7 +3461,7 @@
         <v>120</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P14" s="15">
         <v>1.32E-2</v>
@@ -3482,25 +3485,25 @@
         <v>44</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I15" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="K15" s="45" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="L15" s="20">
         <v>8</v>
@@ -3513,7 +3516,7 @@
         <v>45</v>
       </c>
       <c r="O15" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P15" s="15">
         <v>9.4500000000000001E-2</v>
@@ -3535,25 +3538,25 @@
         <v>45</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I16" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="L16" s="14">
         <v>1</v>
@@ -3566,7 +3569,7 @@
         <v>20</v>
       </c>
       <c r="O16" s="51" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P16" s="15"/>
       <c r="Q16" s="54">
@@ -3588,25 +3591,25 @@
         <v>46</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I17" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="K17" s="45" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="L17" s="20">
         <v>3</v>
@@ -3619,7 +3622,7 @@
         <v>20</v>
       </c>
       <c r="O17" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P17" s="15">
         <v>0.29310000000000003</v>
@@ -3643,25 +3646,25 @@
         <v>47</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I18" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K18" s="44" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="L18" s="14">
         <v>3</v>
@@ -3674,7 +3677,7 @@
         <v>20</v>
       </c>
       <c r="O18" s="51" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P18" s="15">
         <v>3.7199999999999997E-2</v>
@@ -3698,25 +3701,25 @@
         <v>48</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I19" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K19" s="45" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="L19" s="20">
         <v>1</v>
@@ -3729,7 +3732,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="51" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P19" s="21">
         <v>8.6099999999999996E-2</v>
@@ -3753,25 +3756,25 @@
         <v>49</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I20" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="L20" s="14">
         <v>3</v>
@@ -3784,7 +3787,7 @@
         <v>20</v>
       </c>
       <c r="O20" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P20" s="15">
         <v>6.83E-2</v>
@@ -3808,25 +3811,25 @@
         <v>50</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I21" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="K21" s="45" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="L21" s="20">
         <v>2</v>
@@ -3839,7 +3842,7 @@
         <v>100</v>
       </c>
       <c r="O21" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P21" s="15">
         <v>1E-3</v>
@@ -3863,25 +3866,25 @@
         <v>51</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I22" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K22" s="44" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="L22" s="14">
         <v>8</v>
@@ -3894,7 +3897,7 @@
         <v>50</v>
       </c>
       <c r="O22" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P22" s="21">
         <v>8.3999999999999995E-3</v>
@@ -3918,25 +3921,25 @@
         <v>52</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I23" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K23" s="45" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="L23" s="20">
         <v>1</v>
@@ -3949,7 +3952,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="51" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P23" s="21">
         <v>3.8999999999999998E-3</v>
@@ -3973,25 +3976,25 @@
         <v>53</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I24" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K24" s="44" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="L24" s="14">
         <v>1</v>
@@ -4004,7 +4007,7 @@
         <v>100</v>
       </c>
       <c r="O24" s="51" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P24" s="15">
         <v>3.8999999999999998E-3</v>
@@ -4028,25 +4031,25 @@
         <v>54</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I25" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K25" s="45" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="L25" s="20">
         <v>8</v>
@@ -4059,7 +4062,7 @@
         <v>100</v>
       </c>
       <c r="O25" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P25" s="15">
         <v>2.8E-3</v>
@@ -4083,25 +4086,25 @@
         <v>55</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I26" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="L26" s="14">
         <v>1</v>
@@ -4114,7 +4117,7 @@
         <v>50</v>
       </c>
       <c r="O26" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P26" s="21">
         <v>1.4E-2</v>
@@ -4138,25 +4141,25 @@
         <v>56</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I27" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="K27" s="45" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="L27" s="20">
         <v>2</v>
@@ -4169,7 +4172,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P27" s="15">
         <v>2.8E-3</v>
@@ -4193,25 +4196,25 @@
         <v>57</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I28" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="K28" s="44" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="L28" s="14">
         <v>2</v>
@@ -4224,7 +4227,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P28" s="21">
         <v>2.5999999999999999E-3</v>
@@ -4248,25 +4251,25 @@
         <v>58</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I29" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="K29" s="45" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L29" s="20">
         <v>1</v>
@@ -4279,7 +4282,7 @@
         <v>100</v>
       </c>
       <c r="O29" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P29" s="15">
         <v>2.8E-3</v>
@@ -4303,25 +4306,25 @@
         <v>59</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I30" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="K30" s="44" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="L30" s="14">
         <v>2</v>
@@ -4334,7 +4337,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P30" s="21">
         <v>2.5999999999999999E-3</v>
@@ -4358,25 +4361,25 @@
         <v>60</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I31" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="K31" s="45" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="L31" s="20">
         <v>1</v>
@@ -4389,7 +4392,7 @@
         <v>50</v>
       </c>
       <c r="O31" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P31" s="15">
         <v>1.1900000000000001E-2</v>
@@ -4413,25 +4416,25 @@
         <v>61</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I32" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K32" s="44" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L32" s="14">
         <v>2</v>
@@ -4444,7 +4447,7 @@
         <v>100</v>
       </c>
       <c r="O32" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P32" s="21">
         <v>3.0999999999999999E-3</v>
@@ -4468,25 +4471,25 @@
         <v>62</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I33" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="K33" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L33" s="20">
         <v>4</v>
@@ -4499,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="O33" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P33" s="21">
         <v>0.10249999999999999</v>
@@ -4523,25 +4526,25 @@
         <v>63</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I34" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="K34" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L34" s="14">
         <v>2</v>
@@ -4554,7 +4557,7 @@
         <v>20</v>
       </c>
       <c r="O34" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P34" s="21">
         <v>2.4E-2</v>
@@ -4578,25 +4581,25 @@
         <v>64</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I35" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="K35" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L35" s="20">
         <v>10</v>
@@ -4609,7 +4612,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P35" s="21">
         <v>1.29E-2</v>
@@ -4633,25 +4636,25 @@
         <v>65</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I36" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="K36" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L36" s="14">
         <v>1</v>
@@ -4664,7 +4667,7 @@
         <v>10</v>
       </c>
       <c r="O36" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P36" s="15">
         <v>4.53E-2</v>
@@ -4688,25 +4691,25 @@
         <v>66</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I37" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="K37" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L37" s="20">
         <v>1</v>
@@ -4719,7 +4722,7 @@
         <v>10</v>
       </c>
       <c r="O37" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P37" s="21">
         <v>0.153</v>
@@ -4743,25 +4746,25 @@
         <v>67</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I38" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K38" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L38" s="14">
         <v>2</v>
@@ -4774,7 +4777,7 @@
         <v>20</v>
       </c>
       <c r="O38" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P38" s="15">
         <v>3.0800000000000001E-2</v>
@@ -4798,25 +4801,25 @@
         <v>68</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I39" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K39" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L39" s="20">
         <v>2</v>
@@ -4829,7 +4832,7 @@
         <v>15</v>
       </c>
       <c r="O39" s="51" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P39" s="21">
         <v>0.1729</v>
@@ -4853,25 +4856,25 @@
         <v>69</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I40" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="K40" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L40" s="14">
         <v>3</v>
@@ -4884,7 +4887,7 @@
         <v>20</v>
       </c>
       <c r="O40" s="51" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P40" s="15">
         <v>3.5200000000000002E-2</v>
@@ -4908,25 +4911,25 @@
         <v>70</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I41" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="K41" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L41" s="20">
         <v>4</v>
@@ -4939,7 +4942,7 @@
         <v>25</v>
       </c>
       <c r="O41" s="51" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P41" s="21">
         <v>0.1081</v>
@@ -4963,25 +4966,25 @@
         <v>71</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I42" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="K42" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L42" s="14">
         <v>8</v>
@@ -4994,7 +4997,7 @@
         <v>50</v>
       </c>
       <c r="O42" s="51" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P42" s="15">
         <v>5.8900000000000001E-2</v>
@@ -5018,25 +5021,25 @@
         <v>72</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I43" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K43" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L43" s="20">
         <v>2</v>
@@ -5049,7 +5052,7 @@
         <v>50</v>
       </c>
       <c r="O43" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P43" s="15">
         <v>5.5500000000000001E-2</v>
@@ -5073,25 +5076,25 @@
         <v>73</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I44" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K44" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L44" s="14">
         <v>7</v>
@@ -5104,7 +5107,7 @@
         <v>50</v>
       </c>
       <c r="O44" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P44" s="21">
         <v>7.0000000000000001E-3</v>
@@ -5128,25 +5131,25 @@
         <v>74</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I45" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J45" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K45" s="45" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="L45" s="20">
         <v>2</v>
@@ -5159,7 +5162,7 @@
         <v>50</v>
       </c>
       <c r="O45" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P45" s="15">
         <v>1.52E-2</v>
@@ -5183,25 +5186,25 @@
         <v>75</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I46" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="K46" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L46" s="14">
         <v>2</v>
@@ -5214,7 +5217,7 @@
         <v>15</v>
       </c>
       <c r="O46" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P46" s="21">
         <v>0.1482</v>
@@ -5238,25 +5241,25 @@
         <v>76</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I47" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J47" s="20" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="K47" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L47" s="20">
         <v>4</v>
@@ -5269,7 +5272,7 @@
         <v>50</v>
       </c>
       <c r="O47" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P47" s="15">
         <v>1.6899999999999998E-2</v>
@@ -5293,25 +5296,25 @@
         <v>77</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I48" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K48" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L48" s="14">
         <v>1</v>
@@ -5324,7 +5327,7 @@
         <v>12</v>
       </c>
       <c r="O48" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P48" s="21">
         <v>6.4100000000000004E-2</v>
@@ -5348,25 +5351,25 @@
         <v>78</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I49" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J49" s="20" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="K49" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L49" s="20">
         <v>1</v>
@@ -5379,7 +5382,7 @@
         <v>10</v>
       </c>
       <c r="O49" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P49" s="21">
         <v>0.1089</v>
@@ -5403,25 +5406,25 @@
         <v>79</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G50" s="43" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H50" s="14" t="s">
+        <v>643</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="J50" s="14" t="s">
         <v>645</v>
       </c>
-      <c r="I50" s="20" t="s">
-        <v>646</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>647</v>
-      </c>
       <c r="K50" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L50" s="14">
         <v>1</v>
@@ -5434,7 +5437,7 @@
         <v>50</v>
       </c>
       <c r="O50" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P50" s="15">
         <v>1.4500000000000001E-2</v>
@@ -5458,25 +5461,25 @@
         <v>80</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I51" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J51" s="20" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K51" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L51" s="20">
         <v>1</v>
@@ -5489,7 +5492,7 @@
         <v>10</v>
       </c>
       <c r="O51" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P51" s="21">
         <v>6.5199999999999994E-2</v>
@@ -5513,25 +5516,25 @@
         <v>81</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I52" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K52" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L52" s="14">
         <v>1</v>
@@ -5544,7 +5547,7 @@
         <v>20</v>
       </c>
       <c r="O52" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P52" s="15">
         <v>5.1299999999999998E-2</v>
@@ -5568,25 +5571,25 @@
         <v>82</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I53" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J53" s="20" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K53" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L53" s="20">
         <v>1</v>
@@ -5599,7 +5602,7 @@
         <v>10</v>
       </c>
       <c r="O53" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P53" s="21">
         <v>4.2200000000000001E-2</v>
@@ -5623,25 +5626,25 @@
         <v>83</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I54" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K54" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L54" s="14">
         <v>1</v>
@@ -5654,7 +5657,7 @@
         <v>6</v>
       </c>
       <c r="O54" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P54" s="15">
         <v>1.3324</v>
@@ -5678,25 +5681,25 @@
         <v>84</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G55" s="20">
         <v>1715721</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I55" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="K55" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L55" s="20">
         <v>1</v>
@@ -5709,7 +5712,7 @@
         <v>6</v>
       </c>
       <c r="O55" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P55" s="15">
         <v>0.30509999999999998</v>
@@ -5733,25 +5736,25 @@
         <v>85</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I56" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="K56" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L56" s="14">
         <v>7</v>
@@ -5764,7 +5767,7 @@
         <v>40</v>
       </c>
       <c r="O56" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P56" s="15">
         <v>2.7199999999999998E-2</v>
@@ -5788,25 +5791,25 @@
         <v>86</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I57" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J57" s="20" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="K57" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L57" s="20">
         <v>2</v>
@@ -5819,7 +5822,7 @@
         <v>15</v>
       </c>
       <c r="O57" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P57" s="21">
         <v>0.21629999999999999</v>
@@ -5843,25 +5846,25 @@
         <v>87</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I58" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K58" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L58" s="14">
         <v>3</v>
@@ -5874,7 +5877,7 @@
         <v>16</v>
       </c>
       <c r="O58" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P58" s="15">
         <v>1.1589</v>
@@ -5898,25 +5901,25 @@
         <v>88</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="I59" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J59" s="20" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="K59" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L59" s="20">
         <v>1</v>
@@ -5929,7 +5932,7 @@
         <v>6</v>
       </c>
       <c r="O59" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P59" s="21">
         <v>9.7100000000000006E-2</v>
@@ -5953,25 +5956,25 @@
         <v>89</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I60" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K60" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L60" s="14">
         <v>1</v>
@@ -5984,7 +5987,7 @@
         <v>10</v>
       </c>
       <c r="O60" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P60" s="15">
         <v>4.1500000000000002E-2</v>
@@ -6008,25 +6011,25 @@
         <v>90</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I61" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J61" s="20" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K61" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L61" s="20">
         <v>5</v>
@@ -6039,7 +6042,7 @@
         <v>30</v>
       </c>
       <c r="O61" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P61" s="21">
         <v>0.2485</v>
@@ -6063,25 +6066,25 @@
         <v>91</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I62" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="K62" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L62" s="14">
         <v>1</v>
@@ -6094,7 +6097,7 @@
         <v>10</v>
       </c>
       <c r="O62" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P62" s="15">
         <v>9.7799999999999998E-2</v>
@@ -6118,25 +6121,25 @@
         <v>92</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I63" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J63" s="20" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="K63" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L63" s="20">
         <v>1</v>
@@ -6149,7 +6152,7 @@
         <v>100</v>
       </c>
       <c r="O63" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P63" s="21">
         <v>3.3999999999999998E-3</v>
@@ -6173,25 +6176,25 @@
         <v>93</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I64" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K64" s="44" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="L64" s="14">
         <v>1</v>
@@ -6204,7 +6207,7 @@
         <v>10</v>
       </c>
       <c r="O64" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P64" s="15">
         <v>0.35410000000000003</v>
@@ -6228,25 +6231,25 @@
         <v>94</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I65" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J65" s="20" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K65" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L65" s="20">
         <v>4</v>
@@ -6259,7 +6262,7 @@
         <v>40</v>
       </c>
       <c r="O65" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P65" s="15">
         <v>2.2700000000000001E-2</v>
@@ -6280,28 +6283,28 @@
         <v>24</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>95</v>
+        <v>673</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I66" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K66" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L66" s="14">
         <v>2</v>
@@ -6314,7 +6317,7 @@
         <v>20</v>
       </c>
       <c r="O66" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P66" s="21">
         <v>2.3400000000000001E-2</v>
@@ -6335,28 +6338,28 @@
         <v>25</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I67" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J67" s="20" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K67" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L67" s="20">
         <v>1</v>
@@ -6369,7 +6372,7 @@
         <v>50</v>
       </c>
       <c r="O67" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P67" s="15">
         <v>1.6E-2</v>
@@ -6390,28 +6393,28 @@
         <v>25</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H68" s="14" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I68" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K68" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L68" s="14">
         <v>1</v>
@@ -6424,7 +6427,7 @@
         <v>10</v>
       </c>
       <c r="O68" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P68" s="21">
         <v>4.6199999999999998E-2</v>
@@ -6445,28 +6448,28 @@
         <v>25</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="I69" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J69" s="20" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="K69" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L69" s="20">
         <v>1</v>
@@ -6479,7 +6482,7 @@
         <v>50</v>
       </c>
       <c r="O69" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P69" s="21">
         <v>1.6E-2</v>
@@ -6500,28 +6503,28 @@
         <v>26</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H70" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I70" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K70" s="44" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="L70" s="14">
         <v>4</v>
@@ -6534,7 +6537,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P70" s="15">
         <v>6.9999999999999999E-4</v>
@@ -6555,28 +6558,28 @@
         <v>26</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I71" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J71" s="20" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="K71" s="45" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L71" s="20">
         <v>3</v>
@@ -6589,7 +6592,7 @@
         <v>100</v>
       </c>
       <c r="O71" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P71" s="21">
         <v>2.8E-3</v>
@@ -6610,28 +6613,28 @@
         <v>26</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H72" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I72" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="K72" s="44" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="L72" s="14">
         <v>29</v>
@@ -6644,7 +6647,7 @@
         <v>200</v>
       </c>
       <c r="O72" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P72" s="15">
         <v>5.0000000000000001E-4</v>
@@ -6665,28 +6668,28 @@
         <v>27</v>
       </c>
       <c r="D73" s="42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E73" s="42" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F73" s="42" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G73" s="42" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H73" s="42" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I73" s="56" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J73" s="42" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K73" s="46" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="L73" s="42">
         <v>2</v>
@@ -6696,19 +6699,19 @@
         <v>10</v>
       </c>
       <c r="N73" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="O73" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="P73" s="48" t="s">
+        <v>637</v>
+      </c>
+      <c r="Q73" s="54" t="s">
+        <v>637</v>
+      </c>
+      <c r="R73" s="49" t="s">
         <v>639</v>
-      </c>
-      <c r="O73" s="43" t="s">
-        <v>639</v>
-      </c>
-      <c r="P73" s="48" t="s">
-        <v>639</v>
-      </c>
-      <c r="Q73" s="54" t="s">
-        <v>639</v>
-      </c>
-      <c r="R73" s="49" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="60" x14ac:dyDescent="0.25">
@@ -6721,28 +6724,28 @@
         <v>26</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H74" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I74" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K74" s="44" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="L74" s="14">
         <v>25</v>
@@ -6755,7 +6758,7 @@
         <v>200</v>
       </c>
       <c r="O74" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P74" s="15">
         <v>6.9999999999999999E-4</v>
@@ -6776,28 +6779,28 @@
         <v>26</v>
       </c>
       <c r="D75" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E75" s="42" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F75" s="42" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G75" s="42" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H75" s="42" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I75" s="56" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J75" s="42" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K75" s="46" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="L75" s="42">
         <v>2</v>
@@ -6807,19 +6810,19 @@
         <v>10</v>
       </c>
       <c r="N75" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="O75" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="P75" s="48" t="s">
+        <v>637</v>
+      </c>
+      <c r="Q75" s="54" t="s">
+        <v>637</v>
+      </c>
+      <c r="R75" s="49" t="s">
         <v>639</v>
-      </c>
-      <c r="O75" s="43" t="s">
-        <v>639</v>
-      </c>
-      <c r="P75" s="48" t="s">
-        <v>639</v>
-      </c>
-      <c r="Q75" s="54" t="s">
-        <v>639</v>
-      </c>
-      <c r="R75" s="49" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -6832,28 +6835,28 @@
         <v>26</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H76" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I76" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K76" s="44" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="L76" s="14">
         <v>2</v>
@@ -6866,7 +6869,7 @@
         <v>100</v>
       </c>
       <c r="O76" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P76" s="15">
         <v>1E-3</v>
@@ -6887,28 +6890,28 @@
         <v>26</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I77" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J77" s="20" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K77" s="45" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="L77" s="20">
         <v>13</v>
@@ -6921,7 +6924,7 @@
         <v>100</v>
       </c>
       <c r="O77" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P77" s="21">
         <v>6.9999999999999999E-4</v>
@@ -6942,28 +6945,28 @@
         <v>27</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H78" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I78" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K78" s="44" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="L78" s="14">
         <v>34</v>
@@ -6976,7 +6979,7 @@
         <v>200</v>
       </c>
       <c r="O78" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P78" s="15">
         <v>5.9999999999999995E-4</v>
@@ -6997,28 +7000,28 @@
         <v>26</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I79" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J79" s="20" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="K79" s="45" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="L79" s="20">
         <v>1</v>
@@ -7031,7 +7034,7 @@
         <v>20</v>
       </c>
       <c r="O79" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P79" s="21">
         <v>2.7400000000000001E-2</v>
@@ -7052,28 +7055,28 @@
         <v>26</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H80" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I80" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K80" s="44" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="L80" s="14">
         <v>1</v>
@@ -7086,7 +7089,7 @@
         <v>50</v>
       </c>
       <c r="O80" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P80" s="15">
         <v>2.0199999999999999E-2</v>
@@ -7107,28 +7110,28 @@
         <v>26</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I81" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J81" s="20" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K81" s="45" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="L81" s="20">
         <v>1</v>
@@ -7141,7 +7144,7 @@
         <v>100</v>
       </c>
       <c r="O81" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P81" s="21">
         <v>5.9999999999999995E-4</v>
@@ -7162,28 +7165,28 @@
         <v>26</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G82" s="14" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H82" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I82" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="K82" s="44" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="L82" s="14">
         <v>1</v>
@@ -7196,7 +7199,7 @@
         <v>100</v>
       </c>
       <c r="O82" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P82" s="15">
         <v>6.9999999999999999E-4</v>
@@ -7217,28 +7220,28 @@
         <v>26</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I83" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J83" s="20" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K83" s="45" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="L83" s="20">
         <v>1</v>
@@ -7251,7 +7254,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P83" s="15">
         <v>5.9999999999999995E-4</v>
@@ -7272,28 +7275,28 @@
         <v>26</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H84" s="14" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I84" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="K84" s="44" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L84" s="14">
         <v>2</v>
@@ -7306,7 +7309,7 @@
         <v>100</v>
       </c>
       <c r="O84" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P84" s="21">
         <v>6.9999999999999999E-4</v>
@@ -7327,26 +7330,26 @@
         <v>26</v>
       </c>
       <c r="D85" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H85" s="20"/>
       <c r="I85" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J85" s="20" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="K85" s="45" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="L85" s="20">
         <v>4</v>
@@ -7359,7 +7362,7 @@
         <v>100</v>
       </c>
       <c r="O85" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P85" s="15">
         <v>5.9999999999999995E-4</v>
@@ -7380,28 +7383,28 @@
         <v>26</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G86" s="14" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H86" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I86" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K86" s="44" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="L86" s="14">
         <v>2</v>
@@ -7414,7 +7417,7 @@
         <v>100</v>
       </c>
       <c r="O86" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P86" s="21">
         <v>5.9999999999999995E-4</v>
@@ -7435,28 +7438,28 @@
         <v>26</v>
       </c>
       <c r="D87" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I87" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J87" s="20" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="K87" s="45" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="L87" s="20">
         <v>1</v>
@@ -7469,7 +7472,7 @@
         <v>20</v>
       </c>
       <c r="O87" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P87" s="15">
         <v>2.07E-2</v>
@@ -7490,28 +7493,28 @@
         <v>26</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H88" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I88" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="K88" s="44" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="L88" s="14">
         <v>12</v>
@@ -7524,7 +7527,7 @@
         <v>100</v>
       </c>
       <c r="O88" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P88" s="15">
         <v>1.1999999999999999E-3</v>
@@ -7545,28 +7548,28 @@
         <v>26</v>
       </c>
       <c r="D89" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I89" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J89" s="20" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="K89" s="45" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="L89" s="20">
         <v>1</v>
@@ -7579,7 +7582,7 @@
         <v>50</v>
       </c>
       <c r="O89" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P89" s="21">
         <v>1.6799999999999999E-2</v>
@@ -7600,28 +7603,28 @@
         <v>26</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G90" s="14" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H90" s="14" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I90" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="K90" s="44" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="L90" s="14">
         <v>2</v>
@@ -7634,7 +7637,7 @@
         <v>50</v>
       </c>
       <c r="O90" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P90" s="15">
         <v>6.1999999999999998E-3</v>
@@ -7655,28 +7658,28 @@
         <v>26</v>
       </c>
       <c r="D91" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I91" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J91" s="20" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="K91" s="45" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="L91" s="20">
         <v>1</v>
@@ -7689,7 +7692,7 @@
         <v>100</v>
       </c>
       <c r="O91" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P91" s="21">
         <v>1.1000000000000001E-3</v>
@@ -7707,31 +7710,31 @@
         <v>85</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>121</v>
+        <v>674</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="H92" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I92" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="K92" s="44" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L92" s="14">
         <v>1</v>
@@ -7744,457 +7747,457 @@
         <v>100</v>
       </c>
       <c r="O92" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P92" s="15">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q92" s="54">
+        <f>P92*N92</f>
+        <v>0.12</v>
+      </c>
+      <c r="R92" s="14"/>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" s="1"/>
+      <c r="B93" s="16">
+        <f>ROW(B93) - ROW($B$7)</f>
+        <v>86</v>
+      </c>
+      <c r="C93" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E93" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F93" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="G93" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="H93" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="I93" s="55" t="s">
+        <v>651</v>
+      </c>
+      <c r="J93" s="14" t="s">
+        <v>549</v>
+      </c>
+      <c r="K93" s="44" t="s">
+        <v>618</v>
+      </c>
+      <c r="L93" s="14">
+        <v>1</v>
+      </c>
+      <c r="M93" s="14">
+        <f>L93*5</f>
+        <v>5</v>
+      </c>
+      <c r="N93" s="14">
+        <v>100</v>
+      </c>
+      <c r="O93" s="47" t="s">
+        <v>638</v>
+      </c>
+      <c r="P93" s="15">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="Q92" s="54">
+      <c r="Q93" s="54">
         <f t="shared" si="38"/>
         <v>0.4</v>
       </c>
-      <c r="R92" s="14"/>
-    </row>
-    <row r="93" spans="1:18" ht="24" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-      <c r="B93" s="17">
+      <c r="R93" s="14"/>
+    </row>
+    <row r="94" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A94" s="1"/>
+      <c r="B94" s="17">
         <f t="shared" si="0"/>
-        <v>86</v>
-      </c>
-      <c r="C93" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C94" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D93" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E93" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="F93" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="G93" s="20" t="s">
-        <v>399</v>
-      </c>
-      <c r="H93" s="20" t="s">
-        <v>425</v>
-      </c>
-      <c r="I93" s="55" t="s">
-        <v>653</v>
-      </c>
-      <c r="J93" s="20" t="s">
-        <v>552</v>
-      </c>
-      <c r="K93" s="45" t="s">
-        <v>621</v>
-      </c>
-      <c r="L93" s="20">
+      <c r="D94" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="F94" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="G94" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="H94" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="I94" s="55" t="s">
+        <v>651</v>
+      </c>
+      <c r="J94" s="20" t="s">
+        <v>550</v>
+      </c>
+      <c r="K94" s="45" t="s">
+        <v>619</v>
+      </c>
+      <c r="L94" s="20">
         <v>10</v>
       </c>
-      <c r="M93" s="20">
-        <f t="shared" ref="M93" si="46">L93*5</f>
+      <c r="M94" s="20">
+        <f t="shared" ref="M94" si="46">L94*5</f>
         <v>50</v>
       </c>
-      <c r="N93" s="20">
+      <c r="N94" s="20">
         <v>100</v>
       </c>
-      <c r="O93" s="50" t="s">
-        <v>640</v>
-      </c>
-      <c r="P93" s="21">
+      <c r="O94" s="50" t="s">
+        <v>638</v>
+      </c>
+      <c r="P94" s="21">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="Q93" s="54">
+      <c r="Q94" s="54">
         <f t="shared" si="38"/>
         <v>0.09</v>
       </c>
-      <c r="R93" s="20"/>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="B94" s="16">
-        <f>ROW(B94) - ROW($B$7)</f>
-        <v>87</v>
-      </c>
-      <c r="C94" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D94" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="F94" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="G94" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="H94" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="I94" s="55" t="s">
-        <v>653</v>
-      </c>
-      <c r="J94" s="14" t="s">
-        <v>553</v>
-      </c>
-      <c r="K94" s="44" t="s">
-        <v>622</v>
-      </c>
-      <c r="L94" s="14">
-        <v>3</v>
-      </c>
-      <c r="M94" s="14">
-        <f>L94*5</f>
-        <v>15</v>
-      </c>
-      <c r="N94" s="14">
-        <v>100</v>
-      </c>
-      <c r="O94" s="47" t="s">
-        <v>640</v>
-      </c>
-      <c r="P94" s="15">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q94" s="54">
-        <f t="shared" si="38"/>
-        <v>0.11</v>
-      </c>
-      <c r="R94" s="14"/>
+      <c r="R94" s="20"/>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
-      <c r="B95" s="17">
-        <f t="shared" si="0"/>
+      <c r="B95" s="16">
+        <f>ROW(B95) - ROW($B$7)</f>
         <v>88</v>
       </c>
-      <c r="C95" s="23" t="s">
+      <c r="C95" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D95" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E95" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="F95" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="G95" s="20" t="s">
-        <v>401</v>
-      </c>
-      <c r="H95" s="20" t="s">
-        <v>425</v>
+      <c r="D95" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E95" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F95" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="G95" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>423</v>
       </c>
       <c r="I95" s="55" t="s">
-        <v>653</v>
-      </c>
-      <c r="J95" s="20" t="s">
-        <v>554</v>
-      </c>
-      <c r="K95" s="45" t="s">
-        <v>605</v>
-      </c>
-      <c r="L95" s="20">
-        <v>2</v>
-      </c>
-      <c r="M95" s="20">
-        <f t="shared" ref="M95" si="47">L95*5</f>
-        <v>10</v>
-      </c>
-      <c r="N95" s="20">
+        <v>651</v>
+      </c>
+      <c r="J95" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="K95" s="44" t="s">
+        <v>620</v>
+      </c>
+      <c r="L95" s="14">
+        <v>3</v>
+      </c>
+      <c r="M95" s="14">
+        <f>L95*5</f>
+        <v>15</v>
+      </c>
+      <c r="N95" s="14">
         <v>100</v>
       </c>
-      <c r="O95" s="50" t="s">
-        <v>640</v>
-      </c>
-      <c r="P95" s="21">
+      <c r="O95" s="47" t="s">
+        <v>638</v>
+      </c>
+      <c r="P95" s="15">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q95" s="54">
         <f t="shared" si="38"/>
         <v>0.11</v>
       </c>
-      <c r="R95" s="20"/>
+      <c r="R95" s="14"/>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
-      <c r="B96" s="16">
-        <f>ROW(B96) - ROW($B$7)</f>
+      <c r="B96" s="17">
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="C96" s="22" t="s">
+      <c r="C96" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D96" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E96" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="F96" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="G96" s="14" t="s">
-        <v>402</v>
-      </c>
-      <c r="H96" s="14" t="s">
-        <v>425</v>
+      <c r="D96" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F96" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="G96" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="H96" s="20" t="s">
+        <v>423</v>
       </c>
       <c r="I96" s="55" t="s">
-        <v>653</v>
-      </c>
-      <c r="J96" s="14" t="s">
-        <v>555</v>
-      </c>
-      <c r="K96" s="44" t="s">
-        <v>618</v>
-      </c>
-      <c r="L96" s="14">
-        <v>4</v>
-      </c>
-      <c r="M96" s="14">
-        <f>L96*5</f>
-        <v>20</v>
+        <v>651</v>
+      </c>
+      <c r="J96" s="20" t="s">
+        <v>552</v>
+      </c>
+      <c r="K96" s="45" t="s">
+        <v>603</v>
+      </c>
+      <c r="L96" s="20">
+        <v>2</v>
+      </c>
+      <c r="M96" s="20">
+        <f t="shared" ref="M96" si="47">L96*5</f>
+        <v>10</v>
       </c>
       <c r="N96" s="20">
         <v>100</v>
       </c>
-      <c r="O96" s="47" t="s">
-        <v>640</v>
+      <c r="O96" s="50" t="s">
+        <v>638</v>
       </c>
       <c r="P96" s="21">
-        <v>1E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q96" s="54">
         <f t="shared" si="38"/>
-        <v>0.1</v>
-      </c>
-      <c r="R96" s="14"/>
+        <v>0.11</v>
+      </c>
+      <c r="R96" s="20"/>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
-      <c r="B97" s="17">
-        <f t="shared" si="0"/>
+      <c r="B97" s="16">
+        <f>ROW(B97) - ROW($B$7)</f>
         <v>90</v>
       </c>
-      <c r="C97" s="23" t="s">
+      <c r="C97" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D97" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="E97" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="F97" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="G97" s="20" t="s">
-        <v>403</v>
-      </c>
-      <c r="H97" s="20" t="s">
-        <v>425</v>
+      <c r="D97" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E97" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="F97" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="G97" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>423</v>
       </c>
       <c r="I97" s="55" t="s">
-        <v>653</v>
-      </c>
-      <c r="J97" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="K97" s="45" t="s">
-        <v>623</v>
-      </c>
-      <c r="L97" s="20">
-        <v>1</v>
-      </c>
-      <c r="M97" s="20">
-        <f t="shared" ref="M97" si="48">L97*5</f>
-        <v>5</v>
+        <v>651</v>
+      </c>
+      <c r="J97" s="14" t="s">
+        <v>553</v>
+      </c>
+      <c r="K97" s="44" t="s">
+        <v>616</v>
+      </c>
+      <c r="L97" s="14">
+        <v>4</v>
+      </c>
+      <c r="M97" s="14">
+        <f>L97*5</f>
+        <v>20</v>
       </c>
       <c r="N97" s="20">
-        <v>50</v>
-      </c>
-      <c r="O97" s="50" t="s">
-        <v>640</v>
+        <v>100</v>
+      </c>
+      <c r="O97" s="47" t="s">
+        <v>638</v>
       </c>
       <c r="P97" s="21">
-        <v>2.0400000000000001E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="Q97" s="54">
         <f t="shared" si="38"/>
-        <v>1.02</v>
-      </c>
-      <c r="R97" s="20"/>
+        <v>0.1</v>
+      </c>
+      <c r="R97" s="14"/>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
-      <c r="B98" s="16">
-        <f>ROW(B98) - ROW($B$7)</f>
+      <c r="B98" s="17">
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="C98" s="22" t="s">
+      <c r="C98" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D98" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="E98" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="F98" s="42" t="s">
-        <v>300</v>
-      </c>
-      <c r="G98" s="42" t="s">
-        <v>382</v>
-      </c>
-      <c r="H98" s="42" t="s">
-        <v>425</v>
-      </c>
-      <c r="I98" s="56" t="s">
-        <v>653</v>
-      </c>
-      <c r="J98" s="42" t="s">
-        <v>536</v>
-      </c>
-      <c r="K98" s="46" t="s">
-        <v>583</v>
-      </c>
-      <c r="L98" s="42">
+      <c r="D98" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="F98" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="G98" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="H98" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="I98" s="55" t="s">
+        <v>651</v>
+      </c>
+      <c r="J98" s="20" t="s">
+        <v>554</v>
+      </c>
+      <c r="K98" s="45" t="s">
+        <v>621</v>
+      </c>
+      <c r="L98" s="20">
         <v>1</v>
       </c>
-      <c r="M98" s="42">
-        <f>L98*5</f>
+      <c r="M98" s="20">
+        <f t="shared" ref="M98" si="48">L98*5</f>
         <v>5</v>
       </c>
-      <c r="N98" s="43" t="s">
-        <v>639</v>
-      </c>
-      <c r="O98" s="43" t="s">
-        <v>639</v>
-      </c>
-      <c r="P98" s="48" t="s">
-        <v>639</v>
-      </c>
-      <c r="Q98" s="54" t="s">
-        <v>639</v>
-      </c>
-      <c r="R98" s="49" t="s">
-        <v>641</v>
-      </c>
+      <c r="N98" s="20">
+        <v>50</v>
+      </c>
+      <c r="O98" s="50" t="s">
+        <v>638</v>
+      </c>
+      <c r="P98" s="21">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="Q98" s="54">
+        <f t="shared" si="38"/>
+        <v>1.02</v>
+      </c>
+      <c r="R98" s="20"/>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
-      <c r="B99" s="17">
+      <c r="B99" s="16">
+        <f>ROW(B99) - ROW($B$7)</f>
+        <v>92</v>
+      </c>
+      <c r="C99" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D99" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="E99" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="F99" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="G99" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="H99" s="42" t="s">
+        <v>423</v>
+      </c>
+      <c r="I99" s="56" t="s">
+        <v>651</v>
+      </c>
+      <c r="J99" s="42" t="s">
+        <v>534</v>
+      </c>
+      <c r="K99" s="46" t="s">
+        <v>581</v>
+      </c>
+      <c r="L99" s="42">
+        <v>1</v>
+      </c>
+      <c r="M99" s="42">
+        <f>L99*5</f>
+        <v>5</v>
+      </c>
+      <c r="N99" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="O99" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="P99" s="48" t="s">
+        <v>637</v>
+      </c>
+      <c r="Q99" s="54" t="s">
+        <v>637</v>
+      </c>
+      <c r="R99" s="49" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
+      <c r="B100" s="17">
         <f t="shared" si="0"/>
-        <v>92</v>
-      </c>
-      <c r="C99" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C100" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D99" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E99" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="F99" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="G99" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="H99" s="20" t="s">
-        <v>425</v>
-      </c>
-      <c r="I99" s="55" t="s">
-        <v>653</v>
-      </c>
-      <c r="J99" s="20" t="s">
-        <v>557</v>
-      </c>
-      <c r="K99" s="45" t="s">
-        <v>603</v>
-      </c>
-      <c r="L99" s="20">
+      <c r="D100" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="F100" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="G100" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="H100" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="I100" s="55" t="s">
+        <v>651</v>
+      </c>
+      <c r="J100" s="20" t="s">
+        <v>555</v>
+      </c>
+      <c r="K100" s="45" t="s">
+        <v>601</v>
+      </c>
+      <c r="L100" s="20">
         <v>1</v>
       </c>
-      <c r="M99" s="20">
-        <f t="shared" ref="M99" si="49">L99*5</f>
+      <c r="M100" s="20">
+        <f t="shared" ref="M100" si="49">L100*5</f>
         <v>5</v>
       </c>
-      <c r="N99" s="20">
+      <c r="N100" s="20">
         <v>100</v>
       </c>
-      <c r="O99" s="50" t="s">
-        <v>640</v>
-      </c>
-      <c r="P99" s="21">
+      <c r="O100" s="50" t="s">
+        <v>638</v>
+      </c>
+      <c r="P100" s="21">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="Q99" s="54">
+      <c r="Q100" s="54">
         <f t="shared" si="38"/>
         <v>0.09</v>
       </c>
-      <c r="R99" s="20"/>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A100" s="1"/>
-      <c r="B100" s="16">
-        <f>ROW(B100) - ROW($B$7)</f>
-        <v>93</v>
-      </c>
-      <c r="C100" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E100" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="F100" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="G100" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="H100" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="I100" s="55" t="s">
-        <v>653</v>
-      </c>
-      <c r="J100" s="14" t="s">
-        <v>558</v>
-      </c>
-      <c r="K100" s="44" t="s">
-        <v>624</v>
-      </c>
-      <c r="L100" s="14">
-        <v>1</v>
-      </c>
-      <c r="M100" s="14">
-        <f>L100*5</f>
-        <v>5</v>
-      </c>
-      <c r="N100" s="14">
-        <v>100</v>
-      </c>
-      <c r="O100" s="47" t="s">
-        <v>640</v>
-      </c>
-      <c r="P100" s="15">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q100" s="54">
-        <f t="shared" si="38"/>
-        <v>0.12</v>
-      </c>
-      <c r="R100" s="14"/>
+      <c r="R100" s="20"/>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
@@ -8206,28 +8209,28 @@
         <v>28</v>
       </c>
       <c r="D101" s="20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F101" s="20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I101" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J101" s="20" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="K101" s="45" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="L101" s="20">
         <v>3</v>
@@ -8240,7 +8243,7 @@
         <v>50</v>
       </c>
       <c r="O101" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P101" s="21">
         <v>8.2000000000000007E-3</v>
@@ -8261,28 +8264,28 @@
         <v>29</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F102" s="20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G102" s="14" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H102" s="14" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I102" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J102" s="14" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="K102" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L102" s="14">
         <v>3</v>
@@ -8295,7 +8298,7 @@
         <v>20</v>
       </c>
       <c r="O102" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P102" s="15">
         <v>0.1552</v>
@@ -8316,28 +8319,28 @@
         <v>29</v>
       </c>
       <c r="D103" s="20" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F103" s="20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I103" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J103" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K103" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L103" s="20">
         <v>4</v>
@@ -8350,7 +8353,7 @@
         <v>21</v>
       </c>
       <c r="O103" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P103" s="21">
         <v>0.5262</v>
@@ -8371,28 +8374,28 @@
         <v>30</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F104" s="20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G104" s="14" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H104" s="14" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I104" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J104" s="14" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="K104" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L104" s="14">
         <v>1</v>
@@ -8405,7 +8408,7 @@
         <v>6</v>
       </c>
       <c r="O104" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P104" s="15">
         <v>0.36420000000000002</v>
@@ -8426,28 +8429,28 @@
         <v>31</v>
       </c>
       <c r="D105" s="20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F105" s="20" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I105" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J105" s="20" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="K105" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L105" s="20">
         <v>1</v>
@@ -8460,7 +8463,7 @@
         <v>6</v>
       </c>
       <c r="O105" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P105" s="15">
         <v>6.5850999999999997</v>
@@ -8481,28 +8484,28 @@
         <v>32</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G106" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H106" s="14" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I106" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="K106" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L106" s="14">
         <v>1</v>
@@ -8515,7 +8518,7 @@
         <v>6</v>
       </c>
       <c r="O106" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P106" s="21">
         <v>2.6966000000000001</v>
@@ -8536,28 +8539,28 @@
         <v>33</v>
       </c>
       <c r="D107" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F107" s="20" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I107" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J107" s="20" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="K107" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L107" s="20">
         <v>1</v>
@@ -8570,7 +8573,7 @@
         <v>6</v>
       </c>
       <c r="O107" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P107" s="21">
         <v>0.96589999999999998</v>
@@ -8591,28 +8594,28 @@
         <v>33</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G108" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H108" s="14" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I108" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J108" s="14" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="K108" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L108" s="14">
         <v>1</v>
@@ -8625,7 +8628,7 @@
         <v>6</v>
       </c>
       <c r="O108" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P108" s="15">
         <v>1.0339</v>
@@ -8646,28 +8649,28 @@
         <v>33</v>
       </c>
       <c r="D109" s="20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E109" s="20" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F109" s="20" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I109" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J109" s="20" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="K109" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L109" s="20">
         <v>1</v>
@@ -8680,7 +8683,7 @@
         <v>6</v>
       </c>
       <c r="O109" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P109" s="21">
         <v>0.77139999999999997</v>
@@ -8701,28 +8704,28 @@
         <v>33</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G110" s="14" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H110" s="14" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I110" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J110" s="14" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="K110" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L110" s="14">
         <v>1</v>
@@ -8735,7 +8738,7 @@
         <v>6</v>
       </c>
       <c r="O110" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P110" s="15">
         <v>0.40949999999999998</v>
@@ -8756,28 +8759,28 @@
         <v>33</v>
       </c>
       <c r="D111" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I111" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J111" s="20" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="K111" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L111" s="20">
         <v>1</v>
@@ -8790,7 +8793,7 @@
         <v>10</v>
       </c>
       <c r="O111" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P111" s="21">
         <v>0.1729</v>
@@ -8811,28 +8814,28 @@
         <v>33</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G112" s="14" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H112" s="14" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I112" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="K112" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L112" s="14">
         <v>2</v>
@@ -8845,7 +8848,7 @@
         <v>6</v>
       </c>
       <c r="O112" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P112" s="15">
         <v>2.9133</v>
@@ -8866,28 +8869,28 @@
         <v>33</v>
       </c>
       <c r="D113" s="20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F113" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="I113" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J113" s="20" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="K113" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L113" s="20">
         <v>1</v>
@@ -8900,7 +8903,7 @@
         <v>6</v>
       </c>
       <c r="O113" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P113" s="21">
         <v>2.6192000000000002</v>
@@ -8921,28 +8924,28 @@
         <v>34</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G114" s="14" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H114" s="14" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I114" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J114" s="14" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="K114" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L114" s="14">
         <v>1</v>
@@ -8955,7 +8958,7 @@
         <v>10</v>
       </c>
       <c r="O114" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P114" s="15">
         <v>0.28999999999999998</v>
@@ -8976,28 +8979,28 @@
         <v>33</v>
       </c>
       <c r="D115" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F115" s="20" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I115" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J115" s="20" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="K115" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L115" s="20">
         <v>1</v>
@@ -9010,7 +9013,7 @@
         <v>6</v>
       </c>
       <c r="O115" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P115" s="21">
         <v>0.3483</v>
@@ -9031,28 +9034,28 @@
         <v>33</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H116" s="14" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I116" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J116" s="14" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="K116" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L116" s="14">
         <v>1</v>
@@ -9065,7 +9068,7 @@
         <v>6</v>
       </c>
       <c r="O116" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P116" s="21">
         <v>0.33610000000000001</v>
@@ -9086,28 +9089,28 @@
         <v>33</v>
       </c>
       <c r="D117" s="20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E117" s="20" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F117" s="20" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G117" s="20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I117" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J117" s="20" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="K117" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L117" s="20">
         <v>3</v>
@@ -9120,7 +9123,7 @@
         <v>16</v>
       </c>
       <c r="O117" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P117" s="15">
         <v>2.984</v>
@@ -9141,28 +9144,28 @@
         <v>33</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F118" s="14" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G118" s="14" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H118" s="14" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="I118" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J118" s="14" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="K118" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L118" s="14">
         <v>1</v>
@@ -9175,7 +9178,7 @@
         <v>6</v>
       </c>
       <c r="O118" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P118" s="15">
         <v>8.6266999999999996</v>
@@ -9196,28 +9199,28 @@
         <v>33</v>
       </c>
       <c r="D119" s="20" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F119" s="20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G119" s="20" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I119" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J119" s="20" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="K119" s="44" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L119" s="20">
         <v>1</v>
@@ -9230,7 +9233,7 @@
         <v>6</v>
       </c>
       <c r="O119" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P119" s="21">
         <v>0.45850000000000002</v>
@@ -9251,28 +9254,28 @@
         <v>35</v>
       </c>
       <c r="D120" s="43" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E120" s="43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F120" s="42" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G120" s="43" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H120" s="43" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="I120" s="56" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J120" s="43" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="K120" s="46" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="L120" s="43">
         <v>1</v>
@@ -9282,19 +9285,19 @@
         <v>5</v>
       </c>
       <c r="N120" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="O120" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="P120" s="48" t="s">
+        <v>637</v>
+      </c>
+      <c r="Q120" s="54" t="s">
+        <v>637</v>
+      </c>
+      <c r="R120" s="49" t="s">
         <v>639</v>
-      </c>
-      <c r="O120" s="43" t="s">
-        <v>639</v>
-      </c>
-      <c r="P120" s="48" t="s">
-        <v>639</v>
-      </c>
-      <c r="Q120" s="54" t="s">
-        <v>639</v>
-      </c>
-      <c r="R120" s="49" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="121" spans="1:18" ht="24" x14ac:dyDescent="0.25">
@@ -9307,28 +9310,28 @@
         <v>35</v>
       </c>
       <c r="D121" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F121" s="20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H121" s="20" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I121" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J121" s="20" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="K121" s="45" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="L121" s="20">
         <v>1</v>
@@ -9341,7 +9344,7 @@
         <v>10</v>
       </c>
       <c r="O121" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P121" s="21">
         <v>0.30080000000000001</v>
@@ -9362,28 +9365,28 @@
         <v>35</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E122" s="14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F122" s="14" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G122" s="14" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H122" s="14" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I122" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J122" s="14" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="K122" s="44" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="L122" s="14">
         <v>1</v>
@@ -9396,7 +9399,7 @@
         <v>10</v>
       </c>
       <c r="O122" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P122" s="15">
         <v>6.5600000000000006E-2</v>
@@ -9417,28 +9420,28 @@
         <v>35</v>
       </c>
       <c r="D123" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E123" s="20" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F123" s="20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H123" s="20" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="I123" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J123" s="20" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="K123" s="45" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="L123" s="20">
         <v>1</v>
@@ -9451,7 +9454,7 @@
         <v>10</v>
       </c>
       <c r="O123" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P123" s="21">
         <v>0.25950000000000001</v>
@@ -9469,31 +9472,31 @@
         <v>117</v>
       </c>
       <c r="C124" s="23" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D124" s="20" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E124" s="20" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F124" s="20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G124" s="20" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H124" s="20" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="I124" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J124" s="20" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="K124" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L124" s="20">
         <v>1</v>
@@ -9506,7 +9509,7 @@
         <v>5</v>
       </c>
       <c r="O124" s="47" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="P124" s="21">
         <v>7.99</v>
@@ -9524,31 +9527,31 @@
         <v>118</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D125" s="14" t="s">
+        <v>655</v>
+      </c>
+      <c r="E125" s="44" t="s">
+        <v>656</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>636</v>
+      </c>
+      <c r="G125" s="44" t="s">
         <v>657</v>
       </c>
-      <c r="E125" s="44" t="s">
-        <v>658</v>
-      </c>
-      <c r="F125" s="14" t="s">
-        <v>638</v>
-      </c>
-      <c r="G125" s="44" t="s">
-        <v>659</v>
-      </c>
       <c r="H125" s="14" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I125" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J125" s="20" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="K125" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L125" s="20">
         <v>8</v>
@@ -9561,7 +9564,7 @@
         <v>40</v>
       </c>
       <c r="O125" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P125" s="15">
         <v>2.01E-2</v>
@@ -9579,31 +9582,31 @@
         <v>119</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F126" s="14" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G126" s="44">
         <v>50173</v>
       </c>
       <c r="H126" s="14" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="I126" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J126" s="20" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K126" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L126" s="20">
         <v>2</v>
@@ -9616,7 +9619,7 @@
         <v>10</v>
       </c>
       <c r="O126" s="50" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P126" s="15">
         <v>1.3977999999999999</v>
@@ -9634,31 +9637,31 @@
         <v>120</v>
       </c>
       <c r="C127" s="23" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D127" s="20" t="s">
         <v>11</v>
       </c>
       <c r="E127" s="20" t="s">
+        <v>661</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>636</v>
+      </c>
+      <c r="G127" s="20" t="s">
+        <v>662</v>
+      </c>
+      <c r="H127" s="20" t="s">
         <v>663</v>
       </c>
-      <c r="F127" s="14" t="s">
-        <v>638</v>
-      </c>
-      <c r="G127" s="20" t="s">
-        <v>664</v>
-      </c>
-      <c r="H127" s="20" t="s">
-        <v>665</v>
-      </c>
       <c r="I127" s="55" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J127" s="20" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K127" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L127" s="20">
         <v>1</v>
@@ -9671,7 +9674,7 @@
         <v>5</v>
       </c>
       <c r="O127" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P127" s="21">
         <v>8.7099999999999997E-2</v>
@@ -9689,31 +9692,31 @@
         <v>121</v>
       </c>
       <c r="C128" s="23" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D128" s="20" t="s">
+        <v>664</v>
+      </c>
+      <c r="E128" s="20" t="s">
+        <v>665</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>636</v>
+      </c>
+      <c r="G128" s="20" t="s">
         <v>666</v>
       </c>
-      <c r="E128" s="20" t="s">
+      <c r="H128" s="20" t="s">
         <v>667</v>
       </c>
-      <c r="F128" s="14" t="s">
-        <v>638</v>
-      </c>
-      <c r="G128" s="20" t="s">
+      <c r="I128" s="55" t="s">
+        <v>651</v>
+      </c>
+      <c r="J128" s="20" t="s">
         <v>668</v>
       </c>
-      <c r="H128" s="20" t="s">
-        <v>669</v>
-      </c>
-      <c r="I128" s="55" t="s">
-        <v>653</v>
-      </c>
-      <c r="J128" s="20" t="s">
-        <v>670</v>
-      </c>
       <c r="K128" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L128" s="20">
         <v>1</v>
@@ -9726,7 +9729,7 @@
         <v>5</v>
       </c>
       <c r="O128" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P128" s="21">
         <v>1.8872</v>
@@ -9854,7 +9857,7 @@
     <hyperlink ref="O89" r:id="rId55"/>
     <hyperlink ref="O90" r:id="rId56"/>
     <hyperlink ref="O91" r:id="rId57"/>
-    <hyperlink ref="O96" r:id="rId58"/>
+    <hyperlink ref="O97" r:id="rId58"/>
     <hyperlink ref="O101" r:id="rId59"/>
     <hyperlink ref="O102" r:id="rId60"/>
     <hyperlink ref="O103" r:id="rId61"/>
@@ -9894,13 +9897,13 @@
     <hyperlink ref="O78" r:id="rId95"/>
     <hyperlink ref="O79" r:id="rId96"/>
     <hyperlink ref="O80" r:id="rId97"/>
-    <hyperlink ref="O92" r:id="rId98"/>
-    <hyperlink ref="O93" r:id="rId99"/>
-    <hyperlink ref="O94" r:id="rId100"/>
-    <hyperlink ref="O95" r:id="rId101"/>
-    <hyperlink ref="O97" r:id="rId102"/>
-    <hyperlink ref="O99" r:id="rId103"/>
-    <hyperlink ref="O100" r:id="rId104"/>
+    <hyperlink ref="O93" r:id="rId98"/>
+    <hyperlink ref="O94" r:id="rId99"/>
+    <hyperlink ref="O95" r:id="rId100"/>
+    <hyperlink ref="O96" r:id="rId101"/>
+    <hyperlink ref="O98" r:id="rId102"/>
+    <hyperlink ref="O100" r:id="rId103"/>
+    <hyperlink ref="O92" r:id="rId104"/>
     <hyperlink ref="O104" r:id="rId105"/>
     <hyperlink ref="O107" r:id="rId106"/>
     <hyperlink ref="O108" r:id="rId107"/>
